--- a/artfynd/A 1-2025 artfynd.xlsx
+++ b/artfynd/A 1-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122633093</v>
+        <v>122633588</v>
       </c>
       <c r="B2" t="n">
         <v>78656</v>
@@ -711,17 +711,17 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518710</v>
+        <v>518438</v>
       </c>
       <c r="R2" t="n">
-        <v>7077368</v>
+        <v>7077486</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -779,12 +779,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -802,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122630048</v>
+        <v>122632668</v>
       </c>
       <c r="B3" t="n">
-        <v>57333</v>
+        <v>57399</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -814,20 +814,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102621</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -835,39 +835,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518354</v>
+        <v>518751</v>
       </c>
       <c r="R3" t="n">
-        <v>7077408</v>
+        <v>7077424</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -899,6 +885,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska hackspår som bedöms skapade inom 5 år tillbaks. I stambasen av en relativt grov gran.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -907,6 +898,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -923,7 +939,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122630171</v>
+        <v>122630354</v>
       </c>
       <c r="B4" t="n">
         <v>78656</v>
@@ -968,13 +984,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518392</v>
+        <v>518495</v>
       </c>
       <c r="R4" t="n">
-        <v>7077379</v>
+        <v>7077389</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1008,7 +1024,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På flera granar. Vissa bålar är fertila med apothecier.</t>
+          <t>På flera granar. Fertila bålar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1060,7 +1076,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122630221</v>
+        <v>122631313</v>
       </c>
       <c r="B5" t="n">
         <v>57536</v>
@@ -1095,12 +1111,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1109,10 +1125,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518418</v>
+        <v>518757</v>
       </c>
       <c r="R5" t="n">
-        <v>7077502</v>
+        <v>7077459</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1155,6 +1171,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1171,10 +1192,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122632918</v>
+        <v>122633093</v>
       </c>
       <c r="B6" t="n">
-        <v>57536</v>
+        <v>78656</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1187,49 +1208,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518775</v>
+        <v>518710</v>
       </c>
       <c r="R6" t="n">
-        <v>7077267</v>
+        <v>7077368</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1269,6 +1278,31 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1285,10 +1319,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122630809</v>
+        <v>122631152</v>
       </c>
       <c r="B7" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1301,47 +1335,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518650</v>
+        <v>518712</v>
       </c>
       <c r="R7" t="n">
-        <v>7077436</v>
+        <v>7077439</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1373,11 +1397,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1404,12 +1423,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1427,10 +1446,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122630201</v>
+        <v>122632918</v>
       </c>
       <c r="B8" t="n">
-        <v>57383</v>
+        <v>57536</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1443,39 +1462,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518443</v>
+        <v>518775</v>
       </c>
       <c r="R8" t="n">
-        <v>7077513</v>
+        <v>7077267</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1508,11 +1534,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-16</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1539,10 +1560,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122629587</v>
+        <v>122630967</v>
       </c>
       <c r="B9" t="n">
-        <v>57494</v>
+        <v>78656</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1551,50 +1572,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518282</v>
+        <v>518670</v>
       </c>
       <c r="R9" t="n">
-        <v>7077367</v>
+        <v>7077420</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1634,6 +1646,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1650,10 +1687,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122632520</v>
+        <v>122630171</v>
       </c>
       <c r="B10" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1666,39 +1703,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518841</v>
+        <v>518392</v>
       </c>
       <c r="R10" t="n">
-        <v>7077415</v>
+        <v>7077379</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1735,7 +1772,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På flera granar. Vissa bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1746,6 +1783,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1762,10 +1824,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122631152</v>
+        <v>122632510</v>
       </c>
       <c r="B11" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1778,37 +1840,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518712</v>
+        <v>518747</v>
       </c>
       <c r="R11" t="n">
-        <v>7077439</v>
+        <v>7077408</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1840,6 +1907,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Hackspår.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1866,12 +1938,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1889,10 +1961,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122630283</v>
+        <v>122630221</v>
       </c>
       <c r="B12" t="n">
-        <v>78656</v>
+        <v>57536</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1905,34 +1977,43 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518463</v>
+        <v>518418</v>
       </c>
       <c r="R12" t="n">
-        <v>7077394</v>
+        <v>7077502</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1975,31 +2056,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2016,10 +2072,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122630576</v>
+        <v>122632520</v>
       </c>
       <c r="B13" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2032,42 +2088,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518557</v>
+        <v>518841</v>
       </c>
       <c r="R13" t="n">
-        <v>7077475</v>
+        <v>7077415</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2101,7 +2157,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Långväxta bålar och relativt riklig påväxt på flera granar. Fertila bålar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2112,31 +2168,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2153,7 +2184,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122629949</v>
+        <v>122630048</v>
       </c>
       <c r="B14" t="n">
         <v>57333</v>
@@ -2188,12 +2219,22 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>i par</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2202,10 +2243,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>518300</v>
+        <v>518354</v>
       </c>
       <c r="R14" t="n">
-        <v>7077344</v>
+        <v>7077408</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2264,10 +2305,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122633385</v>
+        <v>122630505</v>
       </c>
       <c r="B15" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2280,27 +2321,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2309,10 +2350,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518640</v>
+        <v>518525</v>
       </c>
       <c r="R15" t="n">
-        <v>7077429</v>
+        <v>7077442</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2347,11 +2388,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2360,6 +2396,31 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2376,7 +2437,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122631765</v>
+        <v>122631097</v>
       </c>
       <c r="B16" t="n">
         <v>78656</v>
@@ -2410,16 +2471,21 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518794</v>
+        <v>518656</v>
       </c>
       <c r="R16" t="n">
-        <v>7077456</v>
+        <v>7077425</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2503,10 +2569,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122632510</v>
+        <v>122629587</v>
       </c>
       <c r="B17" t="n">
-        <v>57399</v>
+        <v>57494</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2515,20 +2581,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>103031</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2536,25 +2602,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518747</v>
+        <v>518282</v>
       </c>
       <c r="R17" t="n">
-        <v>7077408</v>
+        <v>7077367</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2586,11 +2656,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Hackspår.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2599,31 +2664,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2640,7 +2680,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122630030</v>
+        <v>122630576</v>
       </c>
       <c r="B18" t="n">
         <v>78656</v>
@@ -2674,19 +2714,24 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518340</v>
+        <v>518557</v>
       </c>
       <c r="R18" t="n">
-        <v>7077417</v>
+        <v>7077475</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2720,7 +2765,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Långväxta bålar och relativt riklig påväxt på flera granar. Fertila bålar.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2772,10 +2817,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122630505</v>
+        <v>122630201</v>
       </c>
       <c r="B19" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2788,27 +2833,27 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2817,10 +2862,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>518525</v>
+        <v>518443</v>
       </c>
       <c r="R19" t="n">
-        <v>7077442</v>
+        <v>7077513</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2855,6 +2900,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2863,31 +2913,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2904,10 +2929,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122633588</v>
+        <v>122633385</v>
       </c>
       <c r="B20" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2920,34 +2945,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>518438</v>
+        <v>518640</v>
       </c>
       <c r="R20" t="n">
-        <v>7077486</v>
+        <v>7077429</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2982,6 +3012,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2990,31 +3025,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3031,7 +3041,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122630967</v>
+        <v>122630030</v>
       </c>
       <c r="B21" t="n">
         <v>78656</v>
@@ -3071,13 +3081,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>518670</v>
+        <v>518340</v>
       </c>
       <c r="R21" t="n">
-        <v>7077420</v>
+        <v>7077417</v>
       </c>
       <c r="S21" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3107,6 +3117,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-02-16</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3158,10 +3173,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122632668</v>
+        <v>122632559</v>
       </c>
       <c r="B22" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3174,39 +3189,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>518751</v>
+        <v>518757</v>
       </c>
       <c r="R22" t="n">
-        <v>7077424</v>
+        <v>7077419</v>
       </c>
       <c r="S22" t="n">
         <v>8</v>
@@ -3241,11 +3251,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färska hackspår som bedöms skapade inom 5 år tillbaks. I stambasen av en relativt grov gran.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3272,12 +3277,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3295,10 +3300,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122631097</v>
+        <v>122629949</v>
       </c>
       <c r="B23" t="n">
-        <v>78656</v>
+        <v>57333</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3307,31 +3312,35 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>102621</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3340,10 +3349,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>518656</v>
+        <v>518300</v>
       </c>
       <c r="R23" t="n">
-        <v>7077425</v>
+        <v>7077344</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3386,31 +3395,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3427,10 +3411,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122630354</v>
+        <v>122630809</v>
       </c>
       <c r="B24" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3443,27 +3427,32 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3472,10 +3461,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>518495</v>
+        <v>518650</v>
       </c>
       <c r="R24" t="n">
-        <v>7077389</v>
+        <v>7077436</v>
       </c>
       <c r="S24" t="n">
         <v>7</v>
@@ -3512,7 +3501,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På flera granar. Fertila bålar.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3541,12 +3530,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3564,7 +3553,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122632559</v>
+        <v>122630283</v>
       </c>
       <c r="B25" t="n">
         <v>78656</v>
@@ -3600,17 +3589,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>518757</v>
+        <v>518463</v>
       </c>
       <c r="R25" t="n">
-        <v>7077419</v>
+        <v>7077394</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3823,10 +3812,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122631313</v>
+        <v>122631765</v>
       </c>
       <c r="B27" t="n">
-        <v>57536</v>
+        <v>78656</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3839,43 +3828,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>518757</v>
+        <v>518794</v>
       </c>
       <c r="R27" t="n">
-        <v>7077459</v>
+        <v>7077456</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3922,6 +3902,26 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>

--- a/artfynd/A 1-2025 artfynd.xlsx
+++ b/artfynd/A 1-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122633588</v>
+        <v>122630283</v>
       </c>
       <c r="B2" t="n">
         <v>78656</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518438</v>
+        <v>518463</v>
       </c>
       <c r="R2" t="n">
-        <v>7077486</v>
+        <v>7077394</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -802,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122632668</v>
+        <v>122631313</v>
       </c>
       <c r="B3" t="n">
-        <v>57399</v>
+        <v>57536</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,42 +818,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518751</v>
+        <v>518757</v>
       </c>
       <c r="R3" t="n">
-        <v>7077424</v>
+        <v>7077459</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,11 +889,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska hackspår som bedöms skapade inom 5 år tillbaks. I stambasen av en relativt grov gran.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -902,26 +901,6 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -939,7 +918,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122630354</v>
+        <v>122630030</v>
       </c>
       <c r="B4" t="n">
         <v>78656</v>
@@ -973,24 +952,19 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518495</v>
+        <v>518340</v>
       </c>
       <c r="R4" t="n">
-        <v>7077389</v>
+        <v>7077417</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1024,7 +998,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På flera granar. Fertila bålar.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1076,10 +1050,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122631313</v>
+        <v>122633385</v>
       </c>
       <c r="B5" t="n">
-        <v>57536</v>
+        <v>57383</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1092,31 +1066,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1125,10 +1095,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518757</v>
+        <v>518640</v>
       </c>
       <c r="R5" t="n">
-        <v>7077459</v>
+        <v>7077429</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1163,6 +1133,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1171,11 +1146,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1192,7 +1162,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122633093</v>
+        <v>122630505</v>
       </c>
       <c r="B6" t="n">
         <v>78656</v>
@@ -1226,19 +1196,24 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518710</v>
+        <v>518525</v>
       </c>
       <c r="R6" t="n">
-        <v>7077368</v>
+        <v>7077442</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1296,12 +1271,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1319,7 +1294,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122631152</v>
+        <v>122630171</v>
       </c>
       <c r="B7" t="n">
         <v>78656</v>
@@ -1353,19 +1328,24 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518712</v>
+        <v>518392</v>
       </c>
       <c r="R7" t="n">
-        <v>7077439</v>
+        <v>7077379</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1395,6 +1375,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-16</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På flera granar. Vissa bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1446,10 +1431,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122632918</v>
+        <v>122631152</v>
       </c>
       <c r="B8" t="n">
-        <v>57536</v>
+        <v>78656</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1462,49 +1447,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518775</v>
+        <v>518712</v>
       </c>
       <c r="R8" t="n">
-        <v>7077267</v>
+        <v>7077439</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1544,6 +1517,31 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1560,10 +1558,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122630967</v>
+        <v>122630221</v>
       </c>
       <c r="B9" t="n">
-        <v>78656</v>
+        <v>57536</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1576,37 +1574,46 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518670</v>
+        <v>518418</v>
       </c>
       <c r="R9" t="n">
-        <v>7077420</v>
+        <v>7077502</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1646,31 +1653,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1687,7 +1669,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122630171</v>
+        <v>122630576</v>
       </c>
       <c r="B10" t="n">
         <v>78656</v>
@@ -1732,13 +1714,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518392</v>
+        <v>518557</v>
       </c>
       <c r="R10" t="n">
-        <v>7077379</v>
+        <v>7077475</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1772,7 +1754,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På flera granar. Vissa bålar är fertila med apothecier.</t>
+          <t>Långväxta bålar och relativt riklig påväxt på flera granar. Fertila bålar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1824,10 +1806,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122632510</v>
+        <v>122630201</v>
       </c>
       <c r="B11" t="n">
-        <v>57399</v>
+        <v>57383</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1840,16 +1822,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1865,17 +1847,17 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518747</v>
+        <v>518443</v>
       </c>
       <c r="R11" t="n">
-        <v>7077408</v>
+        <v>7077513</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1909,7 +1891,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Hackspår.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1920,31 +1902,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1961,10 +1918,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122630221</v>
+        <v>122631097</v>
       </c>
       <c r="B12" t="n">
-        <v>57536</v>
+        <v>78656</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1977,31 +1934,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2010,10 +1963,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518418</v>
+        <v>518656</v>
       </c>
       <c r="R12" t="n">
-        <v>7077502</v>
+        <v>7077425</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2056,6 +2009,31 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2072,10 +2050,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122632520</v>
+        <v>122632918</v>
       </c>
       <c r="B13" t="n">
-        <v>57383</v>
+        <v>57536</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2088,39 +2066,46 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518841</v>
+        <v>518775</v>
       </c>
       <c r="R13" t="n">
-        <v>7077415</v>
+        <v>7077267</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2153,11 +2138,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-16</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2184,10 +2164,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122630048</v>
+        <v>122632520</v>
       </c>
       <c r="B14" t="n">
-        <v>57333</v>
+        <v>57383</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2196,20 +2176,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2217,36 +2197,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>518354</v>
+        <v>518841</v>
       </c>
       <c r="R14" t="n">
-        <v>7077408</v>
+        <v>7077415</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2279,6 +2245,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-16</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2305,7 +2276,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122630505</v>
+        <v>122633588</v>
       </c>
       <c r="B15" t="n">
         <v>78656</v>
@@ -2339,21 +2310,16 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518525</v>
+        <v>518438</v>
       </c>
       <c r="R15" t="n">
-        <v>7077442</v>
+        <v>7077486</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2437,7 +2403,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122631097</v>
+        <v>122630354</v>
       </c>
       <c r="B16" t="n">
         <v>78656</v>
@@ -2482,13 +2448,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518656</v>
+        <v>518495</v>
       </c>
       <c r="R16" t="n">
-        <v>7077425</v>
+        <v>7077389</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2518,6 +2484,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-16</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På flera granar. Fertila bålar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2569,10 +2540,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122629587</v>
+        <v>122633093</v>
       </c>
       <c r="B17" t="n">
-        <v>57494</v>
+        <v>78656</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2581,50 +2552,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518282</v>
+        <v>518710</v>
       </c>
       <c r="R17" t="n">
-        <v>7077367</v>
+        <v>7077368</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2664,6 +2626,31 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2680,10 +2667,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122630576</v>
+        <v>122630048</v>
       </c>
       <c r="B18" t="n">
-        <v>78656</v>
+        <v>57333</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2692,31 +2679,45 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>102621</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2725,13 +2726,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518557</v>
+        <v>518354</v>
       </c>
       <c r="R18" t="n">
-        <v>7077475</v>
+        <v>7077408</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2763,11 +2764,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Långväxta bålar och relativt riklig påväxt på flera granar. Fertila bålar.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2776,31 +2772,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2817,10 +2788,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122630201</v>
+        <v>122632559</v>
       </c>
       <c r="B19" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2833,42 +2804,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>518443</v>
+        <v>518757</v>
       </c>
       <c r="R19" t="n">
-        <v>7077513</v>
+        <v>7077419</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2900,11 +2866,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2913,6 +2874,31 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2929,10 +2915,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122633385</v>
+        <v>122629949</v>
       </c>
       <c r="B20" t="n">
-        <v>57383</v>
+        <v>57333</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2941,20 +2927,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2962,10 +2948,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2974,10 +2964,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>518640</v>
+        <v>518300</v>
       </c>
       <c r="R20" t="n">
-        <v>7077429</v>
+        <v>7077344</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3010,11 +3000,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-02-16</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3041,10 +3026,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122630030</v>
+        <v>122630809</v>
       </c>
       <c r="B21" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3057,37 +3042,47 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>518340</v>
+        <v>518650</v>
       </c>
       <c r="R21" t="n">
-        <v>7077417</v>
+        <v>7077436</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3121,7 +3116,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3150,12 +3145,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3173,7 +3168,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122632559</v>
+        <v>122630967</v>
       </c>
       <c r="B22" t="n">
         <v>78656</v>
@@ -3209,17 +3204,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>518757</v>
+        <v>518670</v>
       </c>
       <c r="R22" t="n">
-        <v>7077419</v>
+        <v>7077420</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3300,10 +3295,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122629949</v>
+        <v>122632668</v>
       </c>
       <c r="B23" t="n">
-        <v>57333</v>
+        <v>57399</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3312,20 +3307,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102621</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3333,29 +3328,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>518300</v>
+        <v>518751</v>
       </c>
       <c r="R23" t="n">
-        <v>7077344</v>
+        <v>7077424</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3387,6 +3378,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska hackspår som bedöms skapade inom 5 år tillbaks. I stambasen av en relativt grov gran.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3395,6 +3391,31 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3411,10 +3432,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122630809</v>
+        <v>122631765</v>
       </c>
       <c r="B24" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3427,47 +3448,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>518650</v>
+        <v>518794</v>
       </c>
       <c r="R24" t="n">
-        <v>7077436</v>
+        <v>7077456</v>
       </c>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3499,11 +3510,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3530,12 +3536,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3553,10 +3559,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122630283</v>
+        <v>122632510</v>
       </c>
       <c r="B25" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3569,37 +3575,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>518463</v>
+        <v>518747</v>
       </c>
       <c r="R25" t="n">
-        <v>7077394</v>
+        <v>7077408</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3631,6 +3642,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Hackspår.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3657,12 +3673,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3812,10 +3828,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122631765</v>
+        <v>122629587</v>
       </c>
       <c r="B27" t="n">
-        <v>78656</v>
+        <v>57494</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3824,38 +3840,47 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>518794</v>
+        <v>518282</v>
       </c>
       <c r="R27" t="n">
-        <v>7077456</v>
+        <v>7077367</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3898,31 +3923,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">

--- a/artfynd/A 1-2025 artfynd.xlsx
+++ b/artfynd/A 1-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122630283</v>
+        <v>122632559</v>
       </c>
       <c r="B2" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -711,17 +711,17 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518463</v>
+        <v>518757</v>
       </c>
       <c r="R2" t="n">
-        <v>7077394</v>
+        <v>7077419</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -802,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122631313</v>
+        <v>122633385</v>
       </c>
       <c r="B3" t="n">
-        <v>57536</v>
+        <v>57384</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,31 +818,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -851,10 +847,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518757</v>
+        <v>518640</v>
       </c>
       <c r="R3" t="n">
-        <v>7077459</v>
+        <v>7077429</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,6 +885,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -897,11 +898,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -918,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122630030</v>
+        <v>122633093</v>
       </c>
       <c r="B4" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -954,17 +950,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518340</v>
+        <v>518710</v>
       </c>
       <c r="R4" t="n">
-        <v>7077417</v>
+        <v>7077368</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -996,11 +992,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1027,12 +1018,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1050,10 +1041,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122633385</v>
+        <v>122630171</v>
       </c>
       <c r="B5" t="n">
-        <v>57383</v>
+        <v>78657</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,27 +1057,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1095,10 +1086,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518640</v>
+        <v>518392</v>
       </c>
       <c r="R5" t="n">
-        <v>7077429</v>
+        <v>7077379</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1135,7 +1126,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På flera granar. Vissa bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,6 +1137,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1162,10 +1178,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122630505</v>
+        <v>122630201</v>
       </c>
       <c r="B6" t="n">
-        <v>78656</v>
+        <v>57384</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1178,27 +1194,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1207,10 +1223,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518525</v>
+        <v>518443</v>
       </c>
       <c r="R6" t="n">
-        <v>7077442</v>
+        <v>7077513</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1245,6 +1261,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1253,31 +1274,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1294,10 +1290,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122630171</v>
+        <v>122632510</v>
       </c>
       <c r="B7" t="n">
-        <v>78656</v>
+        <v>57400</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1310,42 +1306,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518392</v>
+        <v>518747</v>
       </c>
       <c r="R7" t="n">
-        <v>7077379</v>
+        <v>7077408</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1379,7 +1375,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På flera granar. Vissa bålar är fertila med apothecier.</t>
+          <t>Hackspår.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1408,12 +1404,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1431,10 +1427,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122631152</v>
+        <v>122630354</v>
       </c>
       <c r="B8" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1465,19 +1461,24 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518712</v>
+        <v>518495</v>
       </c>
       <c r="R8" t="n">
-        <v>7077439</v>
+        <v>7077389</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1507,6 +1508,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-16</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På flera granar. Fertila bålar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1558,10 +1564,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122630221</v>
+        <v>122630809</v>
       </c>
       <c r="B9" t="n">
-        <v>57536</v>
+        <v>57384</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1574,31 +1580,32 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1607,13 +1614,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518418</v>
+        <v>518650</v>
       </c>
       <c r="R9" t="n">
-        <v>7077502</v>
+        <v>7077436</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1645,6 +1652,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1653,6 +1665,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1669,10 +1706,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122630576</v>
+        <v>122631765</v>
       </c>
       <c r="B10" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1703,24 +1740,19 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518557</v>
+        <v>518794</v>
       </c>
       <c r="R10" t="n">
-        <v>7077475</v>
+        <v>7077456</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1750,11 +1782,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-16</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Långväxta bålar och relativt riklig påväxt på flera granar. Fertila bålar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1806,10 +1833,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122630201</v>
+        <v>122632918</v>
       </c>
       <c r="B11" t="n">
-        <v>57383</v>
+        <v>57537</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1822,39 +1849,46 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518443</v>
+        <v>518775</v>
       </c>
       <c r="R11" t="n">
-        <v>7077513</v>
+        <v>7077267</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1887,11 +1921,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-02-16</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1918,10 +1947,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122631097</v>
+        <v>122631152</v>
       </c>
       <c r="B12" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1952,24 +1981,19 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518656</v>
+        <v>518712</v>
       </c>
       <c r="R12" t="n">
-        <v>7077425</v>
+        <v>7077439</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2050,10 +2074,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122632918</v>
+        <v>122630967</v>
       </c>
       <c r="B13" t="n">
-        <v>57536</v>
+        <v>78657</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2066,49 +2090,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518775</v>
+        <v>518670</v>
       </c>
       <c r="R13" t="n">
-        <v>7077267</v>
+        <v>7077420</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2148,6 +2160,31 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2164,10 +2201,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122632520</v>
+        <v>122633588</v>
       </c>
       <c r="B14" t="n">
-        <v>57383</v>
+        <v>78657</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2180,39 +2217,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>518841</v>
+        <v>518438</v>
       </c>
       <c r="R14" t="n">
-        <v>7077415</v>
+        <v>7077486</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2247,11 +2279,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2260,6 +2287,31 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2276,10 +2328,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122633588</v>
+        <v>122630030</v>
       </c>
       <c r="B15" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2316,10 +2368,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518438</v>
+        <v>518340</v>
       </c>
       <c r="R15" t="n">
-        <v>7077486</v>
+        <v>7077417</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2352,6 +2404,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-16</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2403,10 +2460,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122630354</v>
+        <v>122631097</v>
       </c>
       <c r="B16" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2448,13 +2505,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518495</v>
+        <v>518656</v>
       </c>
       <c r="R16" t="n">
-        <v>7077389</v>
+        <v>7077425</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2484,11 +2541,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-16</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På flera granar. Fertila bålar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2540,10 +2592,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122633093</v>
+        <v>122632668</v>
       </c>
       <c r="B17" t="n">
-        <v>78656</v>
+        <v>57400</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2556,37 +2608,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518710</v>
+        <v>518751</v>
       </c>
       <c r="R17" t="n">
-        <v>7077368</v>
+        <v>7077424</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2618,6 +2675,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska hackspår som bedöms skapade inom 5 år tillbaks. I stambasen av en relativt grov gran.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2644,12 +2706,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2667,10 +2729,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122630048</v>
+        <v>122630221</v>
       </c>
       <c r="B18" t="n">
-        <v>57333</v>
+        <v>57537</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2679,25 +2741,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102621</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2705,19 +2767,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2726,10 +2778,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518354</v>
+        <v>518418</v>
       </c>
       <c r="R18" t="n">
-        <v>7077408</v>
+        <v>7077502</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2788,10 +2840,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122632559</v>
+        <v>122630633</v>
       </c>
       <c r="B19" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2822,19 +2874,24 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>518757</v>
+        <v>518623</v>
       </c>
       <c r="R19" t="n">
-        <v>7077419</v>
+        <v>7077457</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2866,6 +2923,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Relativt rikligt. Fertila bålar.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2890,14 +2952,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2915,10 +2972,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122629949</v>
+        <v>122630283</v>
       </c>
       <c r="B20" t="n">
-        <v>57333</v>
+        <v>78657</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2927,47 +2984,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102621</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>518300</v>
+        <v>518463</v>
       </c>
       <c r="R20" t="n">
-        <v>7077344</v>
+        <v>7077394</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3010,6 +3058,31 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3026,10 +3099,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122630809</v>
+        <v>122630048</v>
       </c>
       <c r="B21" t="n">
-        <v>57383</v>
+        <v>57334</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3038,20 +3111,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3059,15 +3132,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3076,13 +3158,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>518650</v>
+        <v>518354</v>
       </c>
       <c r="R21" t="n">
-        <v>7077436</v>
+        <v>7077408</v>
       </c>
       <c r="S21" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3114,11 +3196,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3127,31 +3204,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3168,10 +3220,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122630967</v>
+        <v>122632520</v>
       </c>
       <c r="B22" t="n">
-        <v>78656</v>
+        <v>57384</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3184,37 +3236,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>518670</v>
+        <v>518841</v>
       </c>
       <c r="R22" t="n">
-        <v>7077420</v>
+        <v>7077415</v>
       </c>
       <c r="S22" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3246,6 +3303,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3254,31 +3316,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3295,10 +3332,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122632668</v>
+        <v>122631313</v>
       </c>
       <c r="B23" t="n">
-        <v>57399</v>
+        <v>57537</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3311,42 +3348,46 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>518751</v>
+        <v>518757</v>
       </c>
       <c r="R23" t="n">
-        <v>7077424</v>
+        <v>7077459</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3378,11 +3419,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska hackspår som bedöms skapade inom 5 år tillbaks. I stambasen av en relativt grov gran.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3395,26 +3431,6 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3432,10 +3448,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122631765</v>
+        <v>122630576</v>
       </c>
       <c r="B24" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3466,19 +3482,24 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>518794</v>
+        <v>518557</v>
       </c>
       <c r="R24" t="n">
-        <v>7077456</v>
+        <v>7077475</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3508,6 +3529,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-02-16</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Långväxta bålar och relativt riklig påväxt på flera granar. Fertila bålar.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3559,10 +3585,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122632510</v>
+        <v>122629949</v>
       </c>
       <c r="B25" t="n">
-        <v>57399</v>
+        <v>57334</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3571,20 +3597,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>102621</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3592,25 +3618,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>518747</v>
+        <v>518300</v>
       </c>
       <c r="R25" t="n">
-        <v>7077408</v>
+        <v>7077344</v>
       </c>
       <c r="S25" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3642,11 +3672,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Hackspår.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3655,31 +3680,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3696,10 +3696,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122630633</v>
+        <v>122629587</v>
       </c>
       <c r="B26" t="n">
-        <v>78656</v>
+        <v>57495</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3708,31 +3708,35 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3741,13 +3745,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>518623</v>
+        <v>518282</v>
       </c>
       <c r="R26" t="n">
-        <v>7077457</v>
+        <v>7077367</v>
       </c>
       <c r="S26" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3779,11 +3783,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Relativt rikligt. Fertila bålar.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3792,26 +3791,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3828,10 +3807,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122629587</v>
+        <v>122630505</v>
       </c>
       <c r="B27" t="n">
-        <v>57494</v>
+        <v>78657</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3840,35 +3819,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3877,10 +3852,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>518282</v>
+        <v>518525</v>
       </c>
       <c r="R27" t="n">
-        <v>7077367</v>
+        <v>7077442</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3923,6 +3898,31 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">

--- a/artfynd/A 1-2025 artfynd.xlsx
+++ b/artfynd/A 1-2025 artfynd.xlsx
@@ -3099,10 +3099,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122630048</v>
+        <v>122632520</v>
       </c>
       <c r="B21" t="n">
-        <v>57334</v>
+        <v>57384</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3111,20 +3111,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3132,36 +3132,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>518354</v>
+        <v>518841</v>
       </c>
       <c r="R21" t="n">
-        <v>7077408</v>
+        <v>7077415</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3194,6 +3180,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-02-16</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3220,10 +3211,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122632520</v>
+        <v>122630048</v>
       </c>
       <c r="B22" t="n">
-        <v>57384</v>
+        <v>57334</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3232,20 +3223,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3253,22 +3244,36 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>518841</v>
+        <v>518354</v>
       </c>
       <c r="R22" t="n">
-        <v>7077415</v>
+        <v>7077408</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3301,11 +3306,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-02-16</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 1-2025 artfynd.xlsx
+++ b/artfynd/A 1-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122632559</v>
       </c>
       <c r="B2" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -802,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122633385</v>
+        <v>122631765</v>
       </c>
       <c r="B3" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,39 +818,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518640</v>
+        <v>518794</v>
       </c>
       <c r="R3" t="n">
-        <v>7077429</v>
+        <v>7077456</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,11 +880,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -898,6 +888,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -914,10 +929,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122633093</v>
+        <v>122630354</v>
       </c>
       <c r="B4" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -948,16 +963,21 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518710</v>
+        <v>518495</v>
       </c>
       <c r="R4" t="n">
-        <v>7077368</v>
+        <v>7077389</v>
       </c>
       <c r="S4" t="n">
         <v>7</v>
@@ -992,6 +1012,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På flera granar. Fertila bålar.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1018,12 +1043,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1041,10 +1066,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122630171</v>
+        <v>122629587</v>
       </c>
       <c r="B5" t="n">
-        <v>78657</v>
+        <v>57495</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1053,31 +1078,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1086,10 +1115,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518392</v>
+        <v>518282</v>
       </c>
       <c r="R5" t="n">
-        <v>7077379</v>
+        <v>7077367</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1124,11 +1153,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På flera granar. Vissa bålar är fertila med apothecier.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1137,31 +1161,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1178,10 +1177,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122630201</v>
+        <v>122631313</v>
       </c>
       <c r="B6" t="n">
-        <v>57384</v>
+        <v>57537</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1194,27 +1193,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1223,10 +1226,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518443</v>
+        <v>518757</v>
       </c>
       <c r="R6" t="n">
-        <v>7077513</v>
+        <v>7077459</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1261,11 +1264,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1274,6 +1272,11 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1290,10 +1293,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122632510</v>
+        <v>122632918</v>
       </c>
       <c r="B7" t="n">
-        <v>57400</v>
+        <v>57537</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1306,42 +1309,49 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518747</v>
+        <v>518775</v>
       </c>
       <c r="R7" t="n">
-        <v>7077408</v>
+        <v>7077267</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1373,11 +1383,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Hackspår.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1386,31 +1391,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1427,10 +1407,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122630354</v>
+        <v>122633093</v>
       </c>
       <c r="B8" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1461,21 +1441,16 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518495</v>
+        <v>518710</v>
       </c>
       <c r="R8" t="n">
-        <v>7077389</v>
+        <v>7077368</v>
       </c>
       <c r="S8" t="n">
         <v>7</v>
@@ -1510,11 +1485,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På flera granar. Fertila bålar.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1541,12 +1511,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1564,10 +1534,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122630809</v>
+        <v>122632510</v>
       </c>
       <c r="B9" t="n">
-        <v>57384</v>
+        <v>57400</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1580,16 +1550,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1603,21 +1573,16 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518650</v>
+        <v>518747</v>
       </c>
       <c r="R9" t="n">
-        <v>7077436</v>
+        <v>7077408</v>
       </c>
       <c r="S9" t="n">
         <v>7</v>
@@ -1654,7 +1619,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Hackspår.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1683,12 +1648,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1706,10 +1671,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122631765</v>
+        <v>122631097</v>
       </c>
       <c r="B10" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1740,16 +1705,21 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518794</v>
+        <v>518656</v>
       </c>
       <c r="R10" t="n">
-        <v>7077456</v>
+        <v>7077425</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1833,10 +1803,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122632918</v>
+        <v>122630967</v>
       </c>
       <c r="B11" t="n">
-        <v>57537</v>
+        <v>78660</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1849,49 +1819,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518775</v>
+        <v>518670</v>
       </c>
       <c r="R11" t="n">
-        <v>7077267</v>
+        <v>7077420</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1931,6 +1889,31 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1950,7 +1933,7 @@
         <v>122631152</v>
       </c>
       <c r="B12" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2074,10 +2057,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122630967</v>
+        <v>122630221</v>
       </c>
       <c r="B13" t="n">
-        <v>78657</v>
+        <v>57537</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2090,37 +2073,46 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518670</v>
+        <v>518418</v>
       </c>
       <c r="R13" t="n">
-        <v>7077420</v>
+        <v>7077502</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2160,31 +2152,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2201,10 +2168,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122633588</v>
+        <v>122630576</v>
       </c>
       <c r="B14" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2235,19 +2202,24 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>518438</v>
+        <v>518557</v>
       </c>
       <c r="R14" t="n">
-        <v>7077486</v>
+        <v>7077475</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2277,6 +2249,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-16</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Långväxta bålar och relativt riklig påväxt på flera granar. Fertila bålar.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2328,10 +2305,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122630030</v>
+        <v>122630505</v>
       </c>
       <c r="B15" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2362,16 +2339,21 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518340</v>
+        <v>518525</v>
       </c>
       <c r="R15" t="n">
-        <v>7077417</v>
+        <v>7077442</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2404,11 +2386,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-16</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2460,10 +2437,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122631097</v>
+        <v>122630633</v>
       </c>
       <c r="B16" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2505,13 +2482,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518656</v>
+        <v>518623</v>
       </c>
       <c r="R16" t="n">
-        <v>7077425</v>
+        <v>7077457</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2543,6 +2520,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Relativt rikligt. Fertila bålar.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2567,14 +2549,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2592,10 +2569,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122632668</v>
+        <v>122632520</v>
       </c>
       <c r="B17" t="n">
-        <v>57400</v>
+        <v>57384</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2608,16 +2585,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2628,7 +2605,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2637,13 +2614,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518751</v>
+        <v>518841</v>
       </c>
       <c r="R17" t="n">
-        <v>7077424</v>
+        <v>7077415</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2677,7 +2654,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Färska hackspår som bedöms skapade inom 5 år tillbaks. I stambasen av en relativt grov gran.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2688,31 +2665,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2729,10 +2681,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122630221</v>
+        <v>122630201</v>
       </c>
       <c r="B18" t="n">
-        <v>57537</v>
+        <v>57384</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2745,31 +2697,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2778,10 +2726,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518418</v>
+        <v>518443</v>
       </c>
       <c r="R18" t="n">
-        <v>7077502</v>
+        <v>7077513</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2814,6 +2762,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-16</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2840,10 +2793,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122630633</v>
+        <v>122632668</v>
       </c>
       <c r="B19" t="n">
-        <v>78657</v>
+        <v>57400</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2856,42 +2809,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>518623</v>
+        <v>518751</v>
       </c>
       <c r="R19" t="n">
-        <v>7077457</v>
+        <v>7077424</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2925,7 +2878,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Relativt rikligt. Fertila bålar.</t>
+          <t>Färska hackspår som bedöms skapade inom 5 år tillbaks. I stambasen av en relativt grov gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2952,9 +2905,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2972,10 +2930,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122630283</v>
+        <v>122630030</v>
       </c>
       <c r="B20" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3012,10 +2970,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>518463</v>
+        <v>518340</v>
       </c>
       <c r="R20" t="n">
-        <v>7077394</v>
+        <v>7077417</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3048,6 +3006,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-02-16</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3099,7 +3062,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122632520</v>
+        <v>122630809</v>
       </c>
       <c r="B21" t="n">
         <v>57384</v>
@@ -3138,19 +3101,24 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>518841</v>
+        <v>518650</v>
       </c>
       <c r="R21" t="n">
-        <v>7077415</v>
+        <v>7077436</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3184,7 +3152,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3195,6 +3163,31 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3211,10 +3204,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122630048</v>
+        <v>122633385</v>
       </c>
       <c r="B22" t="n">
-        <v>57334</v>
+        <v>57384</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3223,20 +3216,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3244,24 +3237,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3270,10 +3249,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>518354</v>
+        <v>518640</v>
       </c>
       <c r="R22" t="n">
-        <v>7077408</v>
+        <v>7077429</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3306,6 +3285,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-02-16</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3332,10 +3316,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122631313</v>
+        <v>122630048</v>
       </c>
       <c r="B23" t="n">
-        <v>57537</v>
+        <v>57334</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3344,35 +3328,45 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>102621</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>i par</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3381,10 +3375,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>518757</v>
+        <v>518354</v>
       </c>
       <c r="R23" t="n">
-        <v>7077459</v>
+        <v>7077408</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3427,11 +3421,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3448,10 +3437,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122630576</v>
+        <v>122630283</v>
       </c>
       <c r="B24" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3482,24 +3471,19 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>518557</v>
+        <v>518463</v>
       </c>
       <c r="R24" t="n">
-        <v>7077475</v>
+        <v>7077394</v>
       </c>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3529,11 +3513,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-02-16</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Långväxta bålar och relativt riklig påväxt på flera granar. Fertila bålar.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3585,10 +3564,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122629949</v>
+        <v>122633588</v>
       </c>
       <c r="B25" t="n">
-        <v>57334</v>
+        <v>78660</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3597,47 +3576,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102621</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>518300</v>
+        <v>518438</v>
       </c>
       <c r="R25" t="n">
-        <v>7077344</v>
+        <v>7077486</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3680,6 +3650,31 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3696,10 +3691,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122629587</v>
+        <v>122630171</v>
       </c>
       <c r="B26" t="n">
-        <v>57495</v>
+        <v>78660</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3708,35 +3703,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3745,10 +3736,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>518282</v>
+        <v>518392</v>
       </c>
       <c r="R26" t="n">
-        <v>7077367</v>
+        <v>7077379</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3783,6 +3774,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På flera granar. Vissa bålar är fertila med apothecier.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3791,6 +3787,31 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3807,10 +3828,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122630505</v>
+        <v>122629949</v>
       </c>
       <c r="B27" t="n">
-        <v>78657</v>
+        <v>57334</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3819,31 +3840,35 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>102621</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3852,10 +3877,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>518525</v>
+        <v>518300</v>
       </c>
       <c r="R27" t="n">
-        <v>7077442</v>
+        <v>7077344</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3898,31 +3923,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">

--- a/artfynd/A 1-2025 artfynd.xlsx
+++ b/artfynd/A 1-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122632559</v>
+        <v>122629587</v>
       </c>
       <c r="B2" t="n">
-        <v>78660</v>
+        <v>57495</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518757</v>
+        <v>518282</v>
       </c>
       <c r="R2" t="n">
-        <v>7077419</v>
+        <v>7077367</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -761,31 +770,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -802,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122631765</v>
+        <v>122630171</v>
       </c>
       <c r="B3" t="n">
         <v>78660</v>
@@ -836,16 +820,21 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518794</v>
+        <v>518392</v>
       </c>
       <c r="R3" t="n">
-        <v>7077456</v>
+        <v>7077379</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,6 +867,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-16</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På flera granar. Vissa bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -929,7 +923,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122630354</v>
+        <v>122630967</v>
       </c>
       <c r="B4" t="n">
         <v>78660</v>
@@ -963,21 +957,16 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518495</v>
+        <v>518670</v>
       </c>
       <c r="R4" t="n">
-        <v>7077389</v>
+        <v>7077420</v>
       </c>
       <c r="S4" t="n">
         <v>7</v>
@@ -1010,11 +999,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-16</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På flera granar. Fertila bålar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1066,10 +1050,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122629587</v>
+        <v>122632520</v>
       </c>
       <c r="B5" t="n">
-        <v>57495</v>
+        <v>57384</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1078,20 +1062,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1099,26 +1083,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518282</v>
+        <v>518841</v>
       </c>
       <c r="R5" t="n">
-        <v>7077367</v>
+        <v>7077415</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1151,6 +1131,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-16</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1177,10 +1162,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122631313</v>
+        <v>122632559</v>
       </c>
       <c r="B6" t="n">
-        <v>57537</v>
+        <v>78660</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1193,46 +1178,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
         <v>518757</v>
       </c>
       <c r="R6" t="n">
-        <v>7077459</v>
+        <v>7077419</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1276,6 +1252,26 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1293,10 +1289,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122632918</v>
+        <v>122630354</v>
       </c>
       <c r="B7" t="n">
-        <v>57537</v>
+        <v>78660</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1309,49 +1305,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518775</v>
+        <v>518495</v>
       </c>
       <c r="R7" t="n">
-        <v>7077267</v>
+        <v>7077389</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1383,6 +1372,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På flera granar. Fertila bålar.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1391,6 +1385,31 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1407,7 +1426,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122633093</v>
+        <v>122630505</v>
       </c>
       <c r="B8" t="n">
         <v>78660</v>
@@ -1441,19 +1460,24 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518710</v>
+        <v>518525</v>
       </c>
       <c r="R8" t="n">
-        <v>7077368</v>
+        <v>7077442</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1511,12 +1535,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1534,10 +1558,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122632510</v>
+        <v>122630576</v>
       </c>
       <c r="B9" t="n">
-        <v>57400</v>
+        <v>78660</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1550,39 +1574,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518747</v>
+        <v>518557</v>
       </c>
       <c r="R9" t="n">
-        <v>7077408</v>
+        <v>7077475</v>
       </c>
       <c r="S9" t="n">
         <v>7</v>
@@ -1619,7 +1643,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Hackspår.</t>
+          <t>Långväxta bålar och relativt riklig påväxt på flera granar. Fertila bålar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1648,12 +1672,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1671,10 +1695,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122631097</v>
+        <v>122630809</v>
       </c>
       <c r="B10" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1687,27 +1711,32 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1716,13 +1745,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518656</v>
+        <v>518650</v>
       </c>
       <c r="R10" t="n">
-        <v>7077425</v>
+        <v>7077436</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1754,6 +1783,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1780,12 +1814,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1803,7 +1837,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122630967</v>
+        <v>122633588</v>
       </c>
       <c r="B11" t="n">
         <v>78660</v>
@@ -1843,13 +1877,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518670</v>
+        <v>518438</v>
       </c>
       <c r="R11" t="n">
-        <v>7077420</v>
+        <v>7077486</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1930,10 +1964,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122631152</v>
+        <v>122632918</v>
       </c>
       <c r="B12" t="n">
-        <v>78660</v>
+        <v>57537</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1946,37 +1980,49 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518712</v>
+        <v>518775</v>
       </c>
       <c r="R12" t="n">
-        <v>7077439</v>
+        <v>7077267</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2016,31 +2062,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2057,10 +2078,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122630221</v>
+        <v>122631765</v>
       </c>
       <c r="B13" t="n">
-        <v>57537</v>
+        <v>78660</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2073,43 +2094,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518418</v>
+        <v>518794</v>
       </c>
       <c r="R13" t="n">
-        <v>7077502</v>
+        <v>7077456</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2152,6 +2164,31 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2168,10 +2205,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122630576</v>
+        <v>122630221</v>
       </c>
       <c r="B14" t="n">
-        <v>78660</v>
+        <v>57537</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2184,27 +2221,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2213,13 +2254,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>518557</v>
+        <v>518418</v>
       </c>
       <c r="R14" t="n">
-        <v>7077475</v>
+        <v>7077502</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2251,11 +2292,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Långväxta bålar och relativt riklig påväxt på flera granar. Fertila bålar.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2264,31 +2300,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2305,10 +2316,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122630505</v>
+        <v>122631313</v>
       </c>
       <c r="B15" t="n">
-        <v>78660</v>
+        <v>57537</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2321,27 +2332,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2350,10 +2365,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518525</v>
+        <v>518757</v>
       </c>
       <c r="R15" t="n">
-        <v>7077442</v>
+        <v>7077459</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2400,26 +2415,6 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2437,7 +2432,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122630633</v>
+        <v>122630030</v>
       </c>
       <c r="B16" t="n">
         <v>78660</v>
@@ -2471,24 +2466,19 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518623</v>
+        <v>518340</v>
       </c>
       <c r="R16" t="n">
-        <v>7077457</v>
+        <v>7077417</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2522,7 +2512,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Relativt rikligt. Fertila bålar.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2549,9 +2539,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2569,10 +2564,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122632520</v>
+        <v>122631097</v>
       </c>
       <c r="B17" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2585,39 +2580,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518841</v>
+        <v>518656</v>
       </c>
       <c r="R17" t="n">
-        <v>7077415</v>
+        <v>7077425</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2652,11 +2647,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2665,6 +2655,31 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2681,10 +2696,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122630201</v>
+        <v>122631152</v>
       </c>
       <c r="B18" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2697,42 +2712,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518443</v>
+        <v>518712</v>
       </c>
       <c r="R18" t="n">
-        <v>7077513</v>
+        <v>7077439</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2764,11 +2774,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2777,6 +2782,31 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2793,10 +2823,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122632668</v>
+        <v>122630201</v>
       </c>
       <c r="B19" t="n">
-        <v>57400</v>
+        <v>57384</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2809,16 +2839,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2829,22 +2859,22 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>518751</v>
+        <v>518443</v>
       </c>
       <c r="R19" t="n">
-        <v>7077424</v>
+        <v>7077513</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2878,7 +2908,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Färska hackspår som bedöms skapade inom 5 år tillbaks. I stambasen av en relativt grov gran.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2889,31 +2919,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2930,7 +2935,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122630030</v>
+        <v>122633093</v>
       </c>
       <c r="B20" t="n">
         <v>78660</v>
@@ -2966,17 +2971,17 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>518340</v>
+        <v>518710</v>
       </c>
       <c r="R20" t="n">
-        <v>7077417</v>
+        <v>7077368</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3008,11 +3013,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3039,12 +3039,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3062,10 +3062,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122630809</v>
+        <v>122632510</v>
       </c>
       <c r="B21" t="n">
-        <v>57384</v>
+        <v>57400</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3078,16 +3078,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3101,21 +3101,16 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>518650</v>
+        <v>518747</v>
       </c>
       <c r="R21" t="n">
-        <v>7077436</v>
+        <v>7077408</v>
       </c>
       <c r="S21" t="n">
         <v>7</v>
@@ -3152,7 +3147,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Hackspår.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3181,12 +3176,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3204,10 +3199,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122633385</v>
+        <v>122629949</v>
       </c>
       <c r="B22" t="n">
-        <v>57384</v>
+        <v>57334</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3216,20 +3211,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3237,10 +3232,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3249,10 +3248,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>518640</v>
+        <v>518300</v>
       </c>
       <c r="R22" t="n">
-        <v>7077429</v>
+        <v>7077344</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3285,11 +3284,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-02-16</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3316,10 +3310,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122630048</v>
+        <v>122630283</v>
       </c>
       <c r="B23" t="n">
-        <v>57334</v>
+        <v>78660</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3328,57 +3322,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102621</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>518354</v>
+        <v>518463</v>
       </c>
       <c r="R23" t="n">
-        <v>7077408</v>
+        <v>7077394</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3421,6 +3396,31 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3437,7 +3437,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122630283</v>
+        <v>122630633</v>
       </c>
       <c r="B24" t="n">
         <v>78660</v>
@@ -3471,19 +3471,24 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>518463</v>
+        <v>518623</v>
       </c>
       <c r="R24" t="n">
-        <v>7077394</v>
+        <v>7077457</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3515,6 +3520,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Relativt rikligt. Fertila bålar.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3539,14 +3549,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3564,10 +3569,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122633588</v>
+        <v>122632668</v>
       </c>
       <c r="B25" t="n">
-        <v>78660</v>
+        <v>57400</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3580,37 +3585,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>518438</v>
+        <v>518751</v>
       </c>
       <c r="R25" t="n">
-        <v>7077486</v>
+        <v>7077424</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3642,6 +3652,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska hackspår som bedöms skapade inom 5 år tillbaks. I stambasen av en relativt grov gran.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3668,12 +3683,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3691,10 +3706,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122630171</v>
+        <v>122633385</v>
       </c>
       <c r="B26" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3707,27 +3722,27 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3736,10 +3751,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>518392</v>
+        <v>518640</v>
       </c>
       <c r="R26" t="n">
-        <v>7077379</v>
+        <v>7077429</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3776,7 +3791,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På flera granar. Vissa bålar är fertila med apothecier.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3787,31 +3802,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3828,7 +3818,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122629949</v>
+        <v>122630048</v>
       </c>
       <c r="B27" t="n">
         <v>57334</v>
@@ -3863,12 +3853,22 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>i par</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>518300</v>
+        <v>518354</v>
       </c>
       <c r="R27" t="n">
-        <v>7077344</v>
+        <v>7077408</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 1-2025 artfynd.xlsx
+++ b/artfynd/A 1-2025 artfynd.xlsx
@@ -2696,10 +2696,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122631152</v>
+        <v>122630201</v>
       </c>
       <c r="B18" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2712,37 +2712,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518712</v>
+        <v>518443</v>
       </c>
       <c r="R18" t="n">
-        <v>7077439</v>
+        <v>7077513</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2774,6 +2779,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2782,31 +2792,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2823,10 +2808,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122630201</v>
+        <v>122631152</v>
       </c>
       <c r="B19" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2839,42 +2824,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>518443</v>
+        <v>518712</v>
       </c>
       <c r="R19" t="n">
-        <v>7077513</v>
+        <v>7077439</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2906,11 +2886,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2919,6 +2894,31 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2935,10 +2935,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122633093</v>
+        <v>122632510</v>
       </c>
       <c r="B20" t="n">
-        <v>78660</v>
+        <v>57400</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2951,34 +2951,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>518710</v>
+        <v>518747</v>
       </c>
       <c r="R20" t="n">
-        <v>7077368</v>
+        <v>7077408</v>
       </c>
       <c r="S20" t="n">
         <v>7</v>
@@ -3013,6 +3018,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Hackspår.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3039,12 +3049,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3062,10 +3072,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122632510</v>
+        <v>122633093</v>
       </c>
       <c r="B21" t="n">
-        <v>57400</v>
+        <v>78660</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3078,39 +3088,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>518747</v>
+        <v>518710</v>
       </c>
       <c r="R21" t="n">
-        <v>7077408</v>
+        <v>7077368</v>
       </c>
       <c r="S21" t="n">
         <v>7</v>
@@ -3145,11 +3150,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Hackspår.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3176,12 +3176,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>

--- a/artfynd/A 1-2025 artfynd.xlsx
+++ b/artfynd/A 1-2025 artfynd.xlsx
@@ -3460,10 +3460,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122630048</v>
+        <v>122633385</v>
       </c>
       <c r="B24" t="n">
-        <v>57428</v>
+        <v>57478</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3472,20 +3472,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3493,24 +3493,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3519,10 +3505,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>518354</v>
+        <v>518640</v>
       </c>
       <c r="R24" t="n">
-        <v>7077408</v>
+        <v>7077429</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3555,6 +3541,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-02-16</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3581,10 +3572,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122633385</v>
+        <v>122630048</v>
       </c>
       <c r="B25" t="n">
-        <v>57478</v>
+        <v>57428</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3593,20 +3584,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3614,10 +3605,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3626,10 +3631,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>518640</v>
+        <v>518354</v>
       </c>
       <c r="R25" t="n">
-        <v>7077429</v>
+        <v>7077408</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3662,11 +3667,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-02-16</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 1-2025 artfynd.xlsx
+++ b/artfynd/A 1-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122632559</v>
+        <v>122630633</v>
       </c>
       <c r="B2" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -709,19 +709,24 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518757</v>
+        <v>518623</v>
       </c>
       <c r="R2" t="n">
-        <v>7077419</v>
+        <v>7077457</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,6 +758,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Relativt rikligt. Fertila bålar.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -777,14 +787,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -802,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122630201</v>
+        <v>122630221</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>57631</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,27 +823,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -847,10 +856,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518443</v>
+        <v>518418</v>
       </c>
       <c r="R3" t="n">
-        <v>7077513</v>
+        <v>7077502</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,11 +892,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-16</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122633093</v>
+        <v>122630967</v>
       </c>
       <c r="B4" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -950,14 +954,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518710</v>
+        <v>518670</v>
       </c>
       <c r="R4" t="n">
-        <v>7077368</v>
+        <v>7077420</v>
       </c>
       <c r="S4" t="n">
         <v>7</v>
@@ -1018,12 +1022,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1041,10 +1045,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122631152</v>
+        <v>122632510</v>
       </c>
       <c r="B5" t="n">
-        <v>78762</v>
+        <v>57494</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1057,37 +1061,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518712</v>
+        <v>518747</v>
       </c>
       <c r="R5" t="n">
-        <v>7077439</v>
+        <v>7077408</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1119,6 +1128,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Hackspår.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1145,12 +1159,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1168,10 +1182,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122630505</v>
+        <v>122631765</v>
       </c>
       <c r="B6" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1202,21 +1216,16 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518525</v>
+        <v>518794</v>
       </c>
       <c r="R6" t="n">
-        <v>7077442</v>
+        <v>7077456</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1300,10 +1309,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122630633</v>
+        <v>122633093</v>
       </c>
       <c r="B7" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1334,21 +1343,16 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518623</v>
+        <v>518710</v>
       </c>
       <c r="R7" t="n">
-        <v>7077457</v>
+        <v>7077368</v>
       </c>
       <c r="S7" t="n">
         <v>7</v>
@@ -1383,11 +1387,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Relativt rikligt. Fertila bålar.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1412,9 +1411,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1432,10 +1436,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122633588</v>
+        <v>122631152</v>
       </c>
       <c r="B8" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1472,13 +1476,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518438</v>
+        <v>518712</v>
       </c>
       <c r="R8" t="n">
-        <v>7077486</v>
+        <v>7077439</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1559,10 +1563,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122630221</v>
+        <v>122632668</v>
       </c>
       <c r="B9" t="n">
-        <v>57631</v>
+        <v>57494</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1575,46 +1579,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518418</v>
+        <v>518751</v>
       </c>
       <c r="R9" t="n">
-        <v>7077502</v>
+        <v>7077424</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1646,6 +1646,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska hackspår som bedöms skapade inom 5 år tillbaks. I stambasen av en relativt grov gran.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1654,6 +1659,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1670,10 +1700,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122630283</v>
+        <v>122633385</v>
       </c>
       <c r="B10" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1686,34 +1716,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518463</v>
+        <v>518640</v>
       </c>
       <c r="R10" t="n">
-        <v>7077394</v>
+        <v>7077429</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1748,6 +1783,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1756,31 +1796,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1797,10 +1812,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122629587</v>
+        <v>122632559</v>
       </c>
       <c r="B11" t="n">
-        <v>57589</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1809,50 +1824,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518282</v>
+        <v>518757</v>
       </c>
       <c r="R11" t="n">
-        <v>7077367</v>
+        <v>7077419</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1892,6 +1898,31 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1908,10 +1939,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122630030</v>
+        <v>122633588</v>
       </c>
       <c r="B12" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1948,10 +1979,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518340</v>
+        <v>518438</v>
       </c>
       <c r="R12" t="n">
-        <v>7077417</v>
+        <v>7077486</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1984,11 +2015,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-16</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2040,10 +2066,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122630171</v>
+        <v>122630809</v>
       </c>
       <c r="B13" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2056,27 +2082,32 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2085,13 +2116,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518392</v>
+        <v>518650</v>
       </c>
       <c r="R13" t="n">
-        <v>7077379</v>
+        <v>7077436</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2125,7 +2156,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På flera granar. Vissa bålar är fertila med apothecier.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2154,12 +2185,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2177,10 +2208,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122630354</v>
+        <v>122631097</v>
       </c>
       <c r="B14" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2222,13 +2253,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>518495</v>
+        <v>518656</v>
       </c>
       <c r="R14" t="n">
-        <v>7077389</v>
+        <v>7077425</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2258,11 +2289,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-16</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På flera granar. Fertila bålar.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2314,10 +2340,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122631765</v>
+        <v>122630201</v>
       </c>
       <c r="B15" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2330,34 +2356,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518794</v>
+        <v>518443</v>
       </c>
       <c r="R15" t="n">
-        <v>7077456</v>
+        <v>7077513</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2392,6 +2423,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2400,31 +2436,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2441,10 +2452,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122631313</v>
+        <v>122630030</v>
       </c>
       <c r="B16" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2457,43 +2468,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518757</v>
+        <v>518340</v>
       </c>
       <c r="R16" t="n">
-        <v>7077459</v>
+        <v>7077417</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2528,6 +2530,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2540,6 +2547,26 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2557,10 +2584,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122630809</v>
+        <v>122630505</v>
       </c>
       <c r="B17" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2573,32 +2600,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2607,13 +2629,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518650</v>
+        <v>518525</v>
       </c>
       <c r="R17" t="n">
-        <v>7077436</v>
+        <v>7077442</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2645,11 +2667,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2676,12 +2693,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2699,10 +2716,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122632520</v>
+        <v>122631313</v>
       </c>
       <c r="B18" t="n">
-        <v>57478</v>
+        <v>57631</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2715,39 +2732,43 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518841</v>
+        <v>518757</v>
       </c>
       <c r="R18" t="n">
-        <v>7077415</v>
+        <v>7077459</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2782,11 +2803,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2795,6 +2811,11 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2811,10 +2832,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122630576</v>
+        <v>122630283</v>
       </c>
       <c r="B19" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2845,24 +2866,19 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>518557</v>
+        <v>518463</v>
       </c>
       <c r="R19" t="n">
-        <v>7077475</v>
+        <v>7077394</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2892,11 +2908,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-02-16</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Långväxta bålar och relativt riklig påväxt på flera granar. Fertila bålar.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2948,10 +2959,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122632668</v>
+        <v>122630171</v>
       </c>
       <c r="B20" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2964,42 +2975,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>518751</v>
+        <v>518392</v>
       </c>
       <c r="R20" t="n">
-        <v>7077424</v>
+        <v>7077379</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3033,7 +3044,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Färska hackspår som bedöms skapade inom 5 år tillbaks. I stambasen av en relativt grov gran.</t>
+          <t>På flera granar. Vissa bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3062,12 +3073,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3085,10 +3096,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122630967</v>
+        <v>122632918</v>
       </c>
       <c r="B21" t="n">
-        <v>78762</v>
+        <v>57631</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3101,37 +3112,49 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>518670</v>
+        <v>518775</v>
       </c>
       <c r="R21" t="n">
-        <v>7077420</v>
+        <v>7077267</v>
       </c>
       <c r="S21" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3171,31 +3194,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3212,10 +3210,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122629949</v>
+        <v>122630354</v>
       </c>
       <c r="B22" t="n">
-        <v>57428</v>
+        <v>78766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3224,35 +3222,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102621</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3261,13 +3255,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>518300</v>
+        <v>518495</v>
       </c>
       <c r="R22" t="n">
-        <v>7077344</v>
+        <v>7077389</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3299,6 +3293,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På flera granar. Fertila bålar.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3307,6 +3306,31 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3323,10 +3347,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122632510</v>
+        <v>122632520</v>
       </c>
       <c r="B23" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3339,16 +3363,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3368,13 +3392,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>518747</v>
+        <v>518841</v>
       </c>
       <c r="R23" t="n">
-        <v>7077408</v>
+        <v>7077415</v>
       </c>
       <c r="S23" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3408,7 +3432,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Hackspår.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3419,31 +3443,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3460,10 +3459,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122633385</v>
+        <v>122629949</v>
       </c>
       <c r="B24" t="n">
-        <v>57478</v>
+        <v>57428</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3472,20 +3471,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3493,10 +3492,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3505,10 +3508,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>518640</v>
+        <v>518300</v>
       </c>
       <c r="R24" t="n">
-        <v>7077429</v>
+        <v>7077344</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3541,11 +3544,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-02-16</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3693,10 +3691,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122631097</v>
+        <v>122630576</v>
       </c>
       <c r="B26" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3738,13 +3736,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>518656</v>
+        <v>518557</v>
       </c>
       <c r="R26" t="n">
-        <v>7077425</v>
+        <v>7077475</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3774,6 +3772,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-02-16</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Långväxta bålar och relativt riklig påväxt på flera granar. Fertila bålar.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3825,10 +3828,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122632918</v>
+        <v>122629587</v>
       </c>
       <c r="B27" t="n">
-        <v>57631</v>
+        <v>57589</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3837,50 +3840,47 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>103031</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>518775</v>
+        <v>518282</v>
       </c>
       <c r="R27" t="n">
-        <v>7077267</v>
+        <v>7077367</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 1-2025 artfynd.xlsx
+++ b/artfynd/A 1-2025 artfynd.xlsx
@@ -1812,10 +1812,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122632559</v>
+        <v>122630809</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1828,37 +1828,47 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518757</v>
+        <v>518650</v>
       </c>
       <c r="R11" t="n">
-        <v>7077419</v>
+        <v>7077436</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1890,6 +1900,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1916,12 +1931,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1939,7 +1954,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122633588</v>
+        <v>122632559</v>
       </c>
       <c r="B12" t="n">
         <v>78766</v>
@@ -1975,17 +1990,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518438</v>
+        <v>518757</v>
       </c>
       <c r="R12" t="n">
-        <v>7077486</v>
+        <v>7077419</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2066,10 +2081,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122630809</v>
+        <v>122633588</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2082,47 +2097,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518650</v>
+        <v>518438</v>
       </c>
       <c r="R13" t="n">
-        <v>7077436</v>
+        <v>7077486</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2154,11 +2159,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2185,12 +2185,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -3210,10 +3210,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122630354</v>
+        <v>122632520</v>
       </c>
       <c r="B22" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3226,42 +3226,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>518495</v>
+        <v>518841</v>
       </c>
       <c r="R22" t="n">
-        <v>7077389</v>
+        <v>7077415</v>
       </c>
       <c r="S22" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På flera granar. Fertila bålar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3306,31 +3306,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3347,10 +3322,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122632520</v>
+        <v>122629949</v>
       </c>
       <c r="B23" t="n">
-        <v>57478</v>
+        <v>57428</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3359,20 +3334,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3380,22 +3355,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>518841</v>
+        <v>518300</v>
       </c>
       <c r="R23" t="n">
-        <v>7077415</v>
+        <v>7077344</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3428,11 +3407,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-02-16</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3459,10 +3433,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122629949</v>
+        <v>122630354</v>
       </c>
       <c r="B24" t="n">
-        <v>57428</v>
+        <v>78766</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3471,35 +3445,31 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102621</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3508,13 +3478,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>518300</v>
+        <v>518495</v>
       </c>
       <c r="R24" t="n">
-        <v>7077344</v>
+        <v>7077389</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3546,6 +3516,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På flera granar. Fertila bålar.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3554,6 +3529,31 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3570,10 +3570,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122630048</v>
+        <v>122630576</v>
       </c>
       <c r="B25" t="n">
-        <v>57428</v>
+        <v>78766</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3582,45 +3582,31 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102621</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3629,13 +3615,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>518354</v>
+        <v>518557</v>
       </c>
       <c r="R25" t="n">
-        <v>7077408</v>
+        <v>7077475</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3667,6 +3653,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Långväxta bålar och relativt riklig påväxt på flera granar. Fertila bålar.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3675,6 +3666,31 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3691,10 +3707,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122630576</v>
+        <v>122630048</v>
       </c>
       <c r="B26" t="n">
-        <v>78766</v>
+        <v>57428</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3703,31 +3719,45 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>102621</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3736,13 +3766,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>518557</v>
+        <v>518354</v>
       </c>
       <c r="R26" t="n">
-        <v>7077475</v>
+        <v>7077408</v>
       </c>
       <c r="S26" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3774,11 +3804,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Långväxta bålar och relativt riklig påväxt på flera granar. Fertila bålar.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3787,31 +3812,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">

--- a/artfynd/A 1-2025 artfynd.xlsx
+++ b/artfynd/A 1-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122630633</v>
+        <v>122631097</v>
       </c>
       <c r="B2" t="n">
         <v>78766</v>
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518623</v>
+        <v>518656</v>
       </c>
       <c r="R2" t="n">
-        <v>7077457</v>
+        <v>7077425</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,11 +758,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Relativt rikligt. Fertila bålar.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -787,9 +782,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -807,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122630221</v>
+        <v>122629587</v>
       </c>
       <c r="B3" t="n">
-        <v>57631</v>
+        <v>57589</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -819,35 +819,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>103031</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518418</v>
+        <v>518282</v>
       </c>
       <c r="R3" t="n">
-        <v>7077502</v>
+        <v>7077367</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -918,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122630967</v>
+        <v>122632510</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,34 +934,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518670</v>
+        <v>518747</v>
       </c>
       <c r="R4" t="n">
-        <v>7077420</v>
+        <v>7077408</v>
       </c>
       <c r="S4" t="n">
         <v>7</v>
@@ -996,6 +1001,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Hackspår.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1022,12 +1032,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1045,10 +1055,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122632510</v>
+        <v>122629949</v>
       </c>
       <c r="B5" t="n">
-        <v>57494</v>
+        <v>57428</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1057,20 +1067,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>102621</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1078,25 +1088,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518747</v>
+        <v>518300</v>
       </c>
       <c r="R5" t="n">
-        <v>7077408</v>
+        <v>7077344</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1128,11 +1142,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Hackspår.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1141,31 +1150,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1182,10 +1166,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122631765</v>
+        <v>122630048</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>57428</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1194,38 +1178,57 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>102621</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518794</v>
+        <v>518354</v>
       </c>
       <c r="R6" t="n">
-        <v>7077456</v>
+        <v>7077408</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1268,31 +1271,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1309,7 +1287,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122633093</v>
+        <v>122632559</v>
       </c>
       <c r="B7" t="n">
         <v>78766</v>
@@ -1349,13 +1327,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518710</v>
+        <v>518757</v>
       </c>
       <c r="R7" t="n">
-        <v>7077368</v>
+        <v>7077419</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1413,12 +1391,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1436,7 +1414,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122631152</v>
+        <v>122630171</v>
       </c>
       <c r="B8" t="n">
         <v>78766</v>
@@ -1470,19 +1448,24 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518712</v>
+        <v>518392</v>
       </c>
       <c r="R8" t="n">
-        <v>7077439</v>
+        <v>7077379</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1512,6 +1495,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-16</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På flera granar. Vissa bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1563,10 +1551,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122632668</v>
+        <v>122631313</v>
       </c>
       <c r="B9" t="n">
-        <v>57494</v>
+        <v>57631</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1579,42 +1567,46 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518751</v>
+        <v>518757</v>
       </c>
       <c r="R9" t="n">
-        <v>7077424</v>
+        <v>7077459</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1646,11 +1638,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska hackspår som bedöms skapade inom 5 år tillbaks. I stambasen av en relativt grov gran.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1663,26 +1650,6 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1700,10 +1667,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122633385</v>
+        <v>122630505</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1716,27 +1683,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1745,10 +1712,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518640</v>
+        <v>518525</v>
       </c>
       <c r="R10" t="n">
-        <v>7077429</v>
+        <v>7077442</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1783,11 +1750,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1796,6 +1758,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1954,7 +1941,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122632559</v>
+        <v>122630576</v>
       </c>
       <c r="B12" t="n">
         <v>78766</v>
@@ -1988,19 +1975,24 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518757</v>
+        <v>518557</v>
       </c>
       <c r="R12" t="n">
-        <v>7077419</v>
+        <v>7077475</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2030,6 +2022,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-16</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Långväxta bålar och relativt riklig påväxt på flera granar. Fertila bålar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2081,10 +2078,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122633588</v>
+        <v>122632918</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2097,34 +2094,46 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518438</v>
+        <v>518775</v>
       </c>
       <c r="R13" t="n">
-        <v>7077486</v>
+        <v>7077267</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2167,31 +2176,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2208,7 +2192,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122631097</v>
+        <v>122630633</v>
       </c>
       <c r="B14" t="n">
         <v>78766</v>
@@ -2253,13 +2237,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>518656</v>
+        <v>518623</v>
       </c>
       <c r="R14" t="n">
-        <v>7077425</v>
+        <v>7077457</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2291,6 +2275,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Relativt rikligt. Fertila bålar.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2315,14 +2304,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2340,7 +2324,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122630201</v>
+        <v>122632520</v>
       </c>
       <c r="B15" t="n">
         <v>57478</v>
@@ -2381,14 +2365,14 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518443</v>
+        <v>518841</v>
       </c>
       <c r="R15" t="n">
-        <v>7077513</v>
+        <v>7077415</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2452,7 +2436,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122630030</v>
+        <v>122630283</v>
       </c>
       <c r="B16" t="n">
         <v>78766</v>
@@ -2492,10 +2476,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518340</v>
+        <v>518463</v>
       </c>
       <c r="R16" t="n">
-        <v>7077417</v>
+        <v>7077394</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2528,11 +2512,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-16</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2584,7 +2563,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122630505</v>
+        <v>122630967</v>
       </c>
       <c r="B17" t="n">
         <v>78766</v>
@@ -2618,24 +2597,19 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518525</v>
+        <v>518670</v>
       </c>
       <c r="R17" t="n">
-        <v>7077442</v>
+        <v>7077420</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2716,10 +2690,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122631313</v>
+        <v>122633385</v>
       </c>
       <c r="B18" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2732,31 +2706,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2765,10 +2735,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518757</v>
+        <v>518640</v>
       </c>
       <c r="R18" t="n">
-        <v>7077459</v>
+        <v>7077429</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2803,6 +2773,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2811,11 +2786,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2832,7 +2802,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122630283</v>
+        <v>122633093</v>
       </c>
       <c r="B19" t="n">
         <v>78766</v>
@@ -2868,17 +2838,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>518463</v>
+        <v>518710</v>
       </c>
       <c r="R19" t="n">
-        <v>7077394</v>
+        <v>7077368</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2936,12 +2906,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2959,10 +2929,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122630171</v>
+        <v>122630201</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2975,27 +2945,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -3004,10 +2974,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>518392</v>
+        <v>518443</v>
       </c>
       <c r="R20" t="n">
-        <v>7077379</v>
+        <v>7077513</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3044,7 +3014,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På flera granar. Vissa bålar är fertila med apothecier.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3055,31 +3025,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3096,10 +3041,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122632918</v>
+        <v>122630354</v>
       </c>
       <c r="B21" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3112,49 +3057,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>518775</v>
+        <v>518495</v>
       </c>
       <c r="R21" t="n">
-        <v>7077267</v>
+        <v>7077389</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3186,6 +3124,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På flera granar. Fertila bålar.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3194,6 +3137,31 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3210,10 +3178,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122632520</v>
+        <v>122633588</v>
       </c>
       <c r="B22" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3226,39 +3194,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>518841</v>
+        <v>518438</v>
       </c>
       <c r="R22" t="n">
-        <v>7077415</v>
+        <v>7077486</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3293,11 +3256,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3306,6 +3264,31 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3322,10 +3305,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122629949</v>
+        <v>122631765</v>
       </c>
       <c r="B23" t="n">
-        <v>57428</v>
+        <v>78766</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3334,47 +3317,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102621</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>518300</v>
+        <v>518794</v>
       </c>
       <c r="R23" t="n">
-        <v>7077344</v>
+        <v>7077456</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3417,6 +3391,31 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3433,10 +3432,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122630354</v>
+        <v>122630221</v>
       </c>
       <c r="B24" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3449,27 +3448,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3478,13 +3481,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>518495</v>
+        <v>518418</v>
       </c>
       <c r="R24" t="n">
-        <v>7077389</v>
+        <v>7077502</v>
       </c>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3516,11 +3519,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På flera granar. Fertila bålar.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3529,31 +3527,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3570,10 +3543,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122630576</v>
+        <v>122632668</v>
       </c>
       <c r="B25" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3586,42 +3559,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>518557</v>
+        <v>518751</v>
       </c>
       <c r="R25" t="n">
-        <v>7077475</v>
+        <v>7077424</v>
       </c>
       <c r="S25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3655,7 +3628,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Långväxta bålar och relativt riklig påväxt på flera granar. Fertila bålar.</t>
+          <t>Färska hackspår som bedöms skapade inom 5 år tillbaks. I stambasen av en relativt grov gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3684,12 +3657,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3707,10 +3680,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122630048</v>
+        <v>122631152</v>
       </c>
       <c r="B26" t="n">
-        <v>57428</v>
+        <v>78766</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3719,60 +3692,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102621</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>518354</v>
+        <v>518712</v>
       </c>
       <c r="R26" t="n">
-        <v>7077408</v>
+        <v>7077439</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3812,6 +3766,31 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3828,10 +3807,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122629587</v>
+        <v>122630030</v>
       </c>
       <c r="B27" t="n">
-        <v>57589</v>
+        <v>78766</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3840,47 +3819,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>518282</v>
+        <v>518340</v>
       </c>
       <c r="R27" t="n">
-        <v>7077367</v>
+        <v>7077417</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3915,6 +3885,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3923,6 +3898,31 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">

--- a/artfynd/A 1-2025 artfynd.xlsx
+++ b/artfynd/A 1-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122631097</v>
+        <v>122630967</v>
       </c>
       <c r="B2" t="n">
         <v>78766</v>
@@ -709,24 +709,19 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518656</v>
+        <v>518670</v>
       </c>
       <c r="R2" t="n">
-        <v>7077425</v>
+        <v>7077420</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -807,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122629587</v>
+        <v>122632668</v>
       </c>
       <c r="B3" t="n">
-        <v>57589</v>
+        <v>57494</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -819,20 +814,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103031</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -840,29 +835,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518282</v>
+        <v>518751</v>
       </c>
       <c r="R3" t="n">
-        <v>7077367</v>
+        <v>7077424</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -894,6 +885,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska hackspår som bedöms skapade inom 5 år tillbaks. I stambasen av en relativt grov gran.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -902,6 +898,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -918,10 +939,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122632510</v>
+        <v>122632520</v>
       </c>
       <c r="B4" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,16 +955,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -963,13 +984,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518747</v>
+        <v>518841</v>
       </c>
       <c r="R4" t="n">
-        <v>7077408</v>
+        <v>7077415</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1003,7 +1024,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Hackspår.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,31 +1035,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1055,10 +1051,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122629949</v>
+        <v>122631765</v>
       </c>
       <c r="B5" t="n">
-        <v>57428</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1067,47 +1063,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102621</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518300</v>
+        <v>518794</v>
       </c>
       <c r="R5" t="n">
-        <v>7077344</v>
+        <v>7077456</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1150,6 +1137,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1166,10 +1178,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122630048</v>
+        <v>122630354</v>
       </c>
       <c r="B6" t="n">
-        <v>57428</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1178,45 +1190,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102621</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1225,13 +1223,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518354</v>
+        <v>518495</v>
       </c>
       <c r="R6" t="n">
-        <v>7077408</v>
+        <v>7077389</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1263,6 +1261,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På flera granar. Fertila bålar.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1271,6 +1274,31 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1287,7 +1315,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122632559</v>
+        <v>122631152</v>
       </c>
       <c r="B7" t="n">
         <v>78766</v>
@@ -1323,14 +1351,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518757</v>
+        <v>518712</v>
       </c>
       <c r="R7" t="n">
-        <v>7077419</v>
+        <v>7077439</v>
       </c>
       <c r="S7" t="n">
         <v>8</v>
@@ -1414,10 +1442,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122630171</v>
+        <v>122631313</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1430,27 +1458,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1459,10 +1491,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518392</v>
+        <v>518757</v>
       </c>
       <c r="R8" t="n">
-        <v>7077379</v>
+        <v>7077459</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1497,11 +1529,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På flera granar. Vissa bålar är fertila med apothecier.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1514,26 +1541,6 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1551,10 +1558,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122631313</v>
+        <v>122630283</v>
       </c>
       <c r="B9" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1567,43 +1574,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518757</v>
+        <v>518463</v>
       </c>
       <c r="R9" t="n">
-        <v>7077459</v>
+        <v>7077394</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1650,6 +1648,26 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1667,7 +1685,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122630505</v>
+        <v>122633093</v>
       </c>
       <c r="B10" t="n">
         <v>78766</v>
@@ -1701,24 +1719,19 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518525</v>
+        <v>518710</v>
       </c>
       <c r="R10" t="n">
-        <v>7077442</v>
+        <v>7077368</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1776,12 +1789,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1941,10 +1954,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122630576</v>
+        <v>122633385</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1957,27 +1970,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1986,13 +1999,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518557</v>
+        <v>518640</v>
       </c>
       <c r="R12" t="n">
-        <v>7077475</v>
+        <v>7077429</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2026,7 +2039,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Långväxta bålar och relativt riklig påväxt på flera granar. Fertila bålar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2037,31 +2050,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2078,10 +2066,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122632918</v>
+        <v>122630633</v>
       </c>
       <c r="B13" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2094,49 +2082,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518775</v>
+        <v>518623</v>
       </c>
       <c r="R13" t="n">
-        <v>7077267</v>
+        <v>7077457</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2168,6 +2149,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Relativt rikligt. Fertila bålar.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2176,6 +2162,26 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2192,7 +2198,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122630633</v>
+        <v>122630576</v>
       </c>
       <c r="B14" t="n">
         <v>78766</v>
@@ -2237,10 +2243,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>518623</v>
+        <v>518557</v>
       </c>
       <c r="R14" t="n">
-        <v>7077457</v>
+        <v>7077475</v>
       </c>
       <c r="S14" t="n">
         <v>7</v>
@@ -2277,7 +2283,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Relativt rikligt. Fertila bålar.</t>
+          <t>Långväxta bålar och relativt riklig påväxt på flera granar. Fertila bålar.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2304,9 +2310,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2324,10 +2335,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122632520</v>
+        <v>122629587</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>57589</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2336,20 +2347,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2357,22 +2368,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518841</v>
+        <v>518282</v>
       </c>
       <c r="R15" t="n">
-        <v>7077415</v>
+        <v>7077367</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2405,11 +2420,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-16</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2436,7 +2446,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122630283</v>
+        <v>122633588</v>
       </c>
       <c r="B16" t="n">
         <v>78766</v>
@@ -2476,10 +2486,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518463</v>
+        <v>518438</v>
       </c>
       <c r="R16" t="n">
-        <v>7077394</v>
+        <v>7077486</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2563,7 +2573,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122630967</v>
+        <v>122630030</v>
       </c>
       <c r="B17" t="n">
         <v>78766</v>
@@ -2603,13 +2613,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518670</v>
+        <v>518340</v>
       </c>
       <c r="R17" t="n">
-        <v>7077420</v>
+        <v>7077417</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2639,6 +2649,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-16</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2690,10 +2705,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122633385</v>
+        <v>122631097</v>
       </c>
       <c r="B18" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2706,27 +2721,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2735,10 +2750,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518640</v>
+        <v>518656</v>
       </c>
       <c r="R18" t="n">
-        <v>7077429</v>
+        <v>7077425</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2773,11 +2788,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2786,6 +2796,31 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2802,10 +2837,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122633093</v>
+        <v>122632510</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2818,34 +2853,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>518710</v>
+        <v>518747</v>
       </c>
       <c r="R19" t="n">
-        <v>7077368</v>
+        <v>7077408</v>
       </c>
       <c r="S19" t="n">
         <v>7</v>
@@ -2880,6 +2920,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Hackspår.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2906,12 +2951,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2929,10 +2974,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122630201</v>
+        <v>122630048</v>
       </c>
       <c r="B20" t="n">
-        <v>57478</v>
+        <v>57428</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2941,20 +2986,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2962,10 +3007,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2974,10 +3033,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>518443</v>
+        <v>518354</v>
       </c>
       <c r="R20" t="n">
-        <v>7077513</v>
+        <v>7077408</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3010,11 +3069,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-02-16</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3041,10 +3095,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122630354</v>
+        <v>122632918</v>
       </c>
       <c r="B21" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3057,42 +3111,49 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>518495</v>
+        <v>518775</v>
       </c>
       <c r="R21" t="n">
-        <v>7077389</v>
+        <v>7077267</v>
       </c>
       <c r="S21" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3124,11 +3185,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På flera granar. Fertila bålar.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3137,31 +3193,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3178,10 +3209,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122633588</v>
+        <v>122629949</v>
       </c>
       <c r="B22" t="n">
-        <v>78766</v>
+        <v>57428</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3190,38 +3221,47 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>102621</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>518438</v>
+        <v>518300</v>
       </c>
       <c r="R22" t="n">
-        <v>7077486</v>
+        <v>7077344</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3264,31 +3304,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3305,10 +3320,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122631765</v>
+        <v>122630221</v>
       </c>
       <c r="B23" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3321,34 +3336,43 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>518794</v>
+        <v>518418</v>
       </c>
       <c r="R23" t="n">
-        <v>7077456</v>
+        <v>7077502</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3391,31 +3415,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3432,10 +3431,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122630221</v>
+        <v>122630171</v>
       </c>
       <c r="B24" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3448,31 +3447,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3481,10 +3476,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>518418</v>
+        <v>518392</v>
       </c>
       <c r="R24" t="n">
-        <v>7077502</v>
+        <v>7077379</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3519,6 +3514,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På flera granar. Vissa bålar är fertila med apothecier.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3527,6 +3527,31 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3543,10 +3568,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122632668</v>
+        <v>122632559</v>
       </c>
       <c r="B25" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3559,39 +3584,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>518751</v>
+        <v>518757</v>
       </c>
       <c r="R25" t="n">
-        <v>7077424</v>
+        <v>7077419</v>
       </c>
       <c r="S25" t="n">
         <v>8</v>
@@ -3626,11 +3646,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färska hackspår som bedöms skapade inom 5 år tillbaks. I stambasen av en relativt grov gran.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3657,12 +3672,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3680,7 +3695,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122631152</v>
+        <v>122630505</v>
       </c>
       <c r="B26" t="n">
         <v>78766</v>
@@ -3714,19 +3729,24 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>518712</v>
+        <v>518525</v>
       </c>
       <c r="R26" t="n">
-        <v>7077439</v>
+        <v>7077442</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3807,10 +3827,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122630030</v>
+        <v>122630201</v>
       </c>
       <c r="B27" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3823,34 +3843,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>518340</v>
+        <v>518443</v>
       </c>
       <c r="R27" t="n">
-        <v>7077417</v>
+        <v>7077513</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3887,7 +3912,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3898,31 +3923,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">

--- a/artfynd/A 1-2025 artfynd.xlsx
+++ b/artfynd/A 1-2025 artfynd.xlsx
@@ -1315,10 +1315,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122631152</v>
+        <v>122631313</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1331,37 +1331,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518712</v>
+        <v>518757</v>
       </c>
       <c r="R7" t="n">
-        <v>7077439</v>
+        <v>7077459</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1405,26 +1414,6 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1442,10 +1431,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122631313</v>
+        <v>122631152</v>
       </c>
       <c r="B8" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1458,46 +1447,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518757</v>
+        <v>518712</v>
       </c>
       <c r="R8" t="n">
-        <v>7077459</v>
+        <v>7077439</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1541,6 +1521,26 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1954,10 +1954,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122633385</v>
+        <v>122630633</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1970,27 +1970,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1999,13 +1999,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518640</v>
+        <v>518623</v>
       </c>
       <c r="R12" t="n">
-        <v>7077429</v>
+        <v>7077457</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Relativt rikligt. Fertila bålar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2050,6 +2050,26 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2066,7 +2086,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122630633</v>
+        <v>122630576</v>
       </c>
       <c r="B13" t="n">
         <v>78766</v>
@@ -2111,10 +2131,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518623</v>
+        <v>518557</v>
       </c>
       <c r="R13" t="n">
-        <v>7077457</v>
+        <v>7077475</v>
       </c>
       <c r="S13" t="n">
         <v>7</v>
@@ -2151,7 +2171,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Relativt rikligt. Fertila bålar.</t>
+          <t>Långväxta bålar och relativt riklig påväxt på flera granar. Fertila bålar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2178,9 +2198,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2198,10 +2223,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122630576</v>
+        <v>122629587</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
+        <v>57589</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2210,31 +2235,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2243,13 +2272,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>518557</v>
+        <v>518282</v>
       </c>
       <c r="R14" t="n">
-        <v>7077475</v>
+        <v>7077367</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2281,11 +2310,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Långväxta bålar och relativt riklig påväxt på flera granar. Fertila bålar.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2294,31 +2318,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2335,10 +2334,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122629587</v>
+        <v>122633588</v>
       </c>
       <c r="B15" t="n">
-        <v>57589</v>
+        <v>78766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2347,47 +2346,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518282</v>
+        <v>518438</v>
       </c>
       <c r="R15" t="n">
-        <v>7077367</v>
+        <v>7077486</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2430,6 +2420,31 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2446,7 +2461,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122633588</v>
+        <v>122630030</v>
       </c>
       <c r="B16" t="n">
         <v>78766</v>
@@ -2486,10 +2501,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518438</v>
+        <v>518340</v>
       </c>
       <c r="R16" t="n">
-        <v>7077486</v>
+        <v>7077417</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2522,6 +2537,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-16</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2573,7 +2593,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122630030</v>
+        <v>122631097</v>
       </c>
       <c r="B17" t="n">
         <v>78766</v>
@@ -2607,16 +2627,21 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518340</v>
+        <v>518656</v>
       </c>
       <c r="R17" t="n">
-        <v>7077417</v>
+        <v>7077425</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2649,11 +2674,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-16</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2705,10 +2725,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122631097</v>
+        <v>122632510</v>
       </c>
       <c r="B18" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2721,42 +2741,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518656</v>
+        <v>518747</v>
       </c>
       <c r="R18" t="n">
-        <v>7077425</v>
+        <v>7077408</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2788,6 +2808,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Hackspår.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2814,12 +2839,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2837,10 +2862,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122632510</v>
+        <v>122630048</v>
       </c>
       <c r="B19" t="n">
-        <v>57494</v>
+        <v>57428</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2849,20 +2874,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>102621</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2870,25 +2895,39 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>518747</v>
+        <v>518354</v>
       </c>
       <c r="R19" t="n">
         <v>7077408</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2920,11 +2959,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Hackspår.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2933,31 +2967,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2974,7 +2983,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122630048</v>
+        <v>122629949</v>
       </c>
       <c r="B20" t="n">
         <v>57428</v>
@@ -3009,22 +3018,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>i par</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -3033,10 +3032,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>518354</v>
+        <v>518300</v>
       </c>
       <c r="R20" t="n">
-        <v>7077408</v>
+        <v>7077344</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3209,10 +3208,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122629949</v>
+        <v>122630221</v>
       </c>
       <c r="B22" t="n">
-        <v>57428</v>
+        <v>57631</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3221,35 +3220,35 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102621</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3258,10 +3257,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>518300</v>
+        <v>518418</v>
       </c>
       <c r="R22" t="n">
-        <v>7077344</v>
+        <v>7077502</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3320,10 +3319,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122630221</v>
+        <v>122630171</v>
       </c>
       <c r="B23" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3336,31 +3335,27 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3369,10 +3364,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>518418</v>
+        <v>518392</v>
       </c>
       <c r="R23" t="n">
-        <v>7077502</v>
+        <v>7077379</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3407,6 +3402,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På flera granar. Vissa bålar är fertila med apothecier.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3415,6 +3415,31 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3431,7 +3456,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122630171</v>
+        <v>122632559</v>
       </c>
       <c r="B24" t="n">
         <v>78766</v>
@@ -3465,24 +3490,19 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>518392</v>
+        <v>518757</v>
       </c>
       <c r="R24" t="n">
-        <v>7077379</v>
+        <v>7077419</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3512,11 +3532,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-02-16</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På flera granar. Vissa bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3568,7 +3583,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122632559</v>
+        <v>122630505</v>
       </c>
       <c r="B25" t="n">
         <v>78766</v>
@@ -3602,19 +3617,24 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>518757</v>
+        <v>518525</v>
       </c>
       <c r="R25" t="n">
-        <v>7077419</v>
+        <v>7077442</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3695,10 +3715,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122630505</v>
+        <v>122630201</v>
       </c>
       <c r="B26" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3711,27 +3731,27 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3740,10 +3760,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>518525</v>
+        <v>518443</v>
       </c>
       <c r="R26" t="n">
-        <v>7077442</v>
+        <v>7077513</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3778,6 +3798,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3786,31 +3811,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3827,7 +3827,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122630201</v>
+        <v>122633385</v>
       </c>
       <c r="B27" t="n">
         <v>57478</v>
@@ -3872,10 +3872,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>518443</v>
+        <v>518640</v>
       </c>
       <c r="R27" t="n">
-        <v>7077513</v>
+        <v>7077429</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 1-2025 artfynd.xlsx
+++ b/artfynd/A 1-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122630967</v>
+        <v>122630171</v>
       </c>
       <c r="B2" t="n">
         <v>78766</v>
@@ -709,19 +709,24 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518670</v>
+        <v>518392</v>
       </c>
       <c r="R2" t="n">
-        <v>7077420</v>
+        <v>7077379</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,6 +756,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-16</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På flera granar. Vissa bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -802,10 +812,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122632668</v>
+        <v>122632918</v>
       </c>
       <c r="B3" t="n">
-        <v>57494</v>
+        <v>57631</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,42 +828,49 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518751</v>
+        <v>518775</v>
       </c>
       <c r="R3" t="n">
-        <v>7077424</v>
+        <v>7077267</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,11 +902,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska hackspår som bedöms skapade inom 5 år tillbaks. I stambasen av en relativt grov gran.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -898,31 +910,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -939,10 +926,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122632520</v>
+        <v>122630048</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>57428</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -951,20 +938,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -972,22 +959,36 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518841</v>
+        <v>518354</v>
       </c>
       <c r="R4" t="n">
-        <v>7077415</v>
+        <v>7077408</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,11 +1021,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-16</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1051,7 +1047,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122631765</v>
+        <v>122632559</v>
       </c>
       <c r="B5" t="n">
         <v>78766</v>
@@ -1091,13 +1087,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518794</v>
+        <v>518757</v>
       </c>
       <c r="R5" t="n">
-        <v>7077456</v>
+        <v>7077419</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1178,7 +1174,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122630354</v>
+        <v>122630576</v>
       </c>
       <c r="B6" t="n">
         <v>78766</v>
@@ -1223,10 +1219,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518495</v>
+        <v>518557</v>
       </c>
       <c r="R6" t="n">
-        <v>7077389</v>
+        <v>7077475</v>
       </c>
       <c r="S6" t="n">
         <v>7</v>
@@ -1263,7 +1259,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På flera granar. Fertila bålar.</t>
+          <t>Långväxta bålar och relativt riklig påväxt på flera granar. Fertila bålar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1315,10 +1311,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122631313</v>
+        <v>122630201</v>
       </c>
       <c r="B7" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1331,31 +1327,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1364,10 +1356,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518757</v>
+        <v>518443</v>
       </c>
       <c r="R7" t="n">
-        <v>7077459</v>
+        <v>7077513</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1402,6 +1394,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1410,11 +1407,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1431,10 +1423,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122631152</v>
+        <v>122632668</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1447,34 +1439,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518712</v>
+        <v>518751</v>
       </c>
       <c r="R8" t="n">
-        <v>7077439</v>
+        <v>7077424</v>
       </c>
       <c r="S8" t="n">
         <v>8</v>
@@ -1509,6 +1506,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska hackspår som bedöms skapade inom 5 år tillbaks. I stambasen av en relativt grov gran.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1535,12 +1537,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1558,7 +1560,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122630283</v>
+        <v>122630505</v>
       </c>
       <c r="B9" t="n">
         <v>78766</v>
@@ -1592,16 +1594,21 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518463</v>
+        <v>518525</v>
       </c>
       <c r="R9" t="n">
-        <v>7077394</v>
+        <v>7077442</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1685,10 +1692,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122633093</v>
+        <v>122631313</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1701,37 +1708,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518710</v>
+        <v>518757</v>
       </c>
       <c r="R10" t="n">
-        <v>7077368</v>
+        <v>7077459</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1775,26 +1791,6 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1812,10 +1808,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122630809</v>
+        <v>122630283</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1828,47 +1824,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518650</v>
+        <v>518463</v>
       </c>
       <c r="R11" t="n">
-        <v>7077436</v>
+        <v>7077394</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1900,11 +1886,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1931,12 +1912,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1954,10 +1935,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122630633</v>
+        <v>122632520</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1970,42 +1951,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518623</v>
+        <v>518841</v>
       </c>
       <c r="R12" t="n">
-        <v>7077457</v>
+        <v>7077415</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2039,7 +2020,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Relativt rikligt. Fertila bålar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2050,26 +2031,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2086,10 +2047,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122630576</v>
+        <v>122629587</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>57589</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2098,31 +2059,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2131,13 +2096,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518557</v>
+        <v>518282</v>
       </c>
       <c r="R13" t="n">
-        <v>7077475</v>
+        <v>7077367</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2169,11 +2134,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Långväxta bålar och relativt riklig påväxt på flera granar. Fertila bålar.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2182,31 +2142,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2223,10 +2158,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122629587</v>
+        <v>122631097</v>
       </c>
       <c r="B14" t="n">
-        <v>57589</v>
+        <v>78766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2235,35 +2170,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2272,10 +2203,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>518282</v>
+        <v>518656</v>
       </c>
       <c r="R14" t="n">
-        <v>7077367</v>
+        <v>7077425</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2318,6 +2249,31 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2334,7 +2290,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122633588</v>
+        <v>122630967</v>
       </c>
       <c r="B15" t="n">
         <v>78766</v>
@@ -2374,13 +2330,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518438</v>
+        <v>518670</v>
       </c>
       <c r="R15" t="n">
-        <v>7077486</v>
+        <v>7077420</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2461,7 +2417,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122630030</v>
+        <v>122631152</v>
       </c>
       <c r="B16" t="n">
         <v>78766</v>
@@ -2501,13 +2457,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518340</v>
+        <v>518712</v>
       </c>
       <c r="R16" t="n">
-        <v>7077417</v>
+        <v>7077439</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2537,11 +2493,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-16</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2593,10 +2544,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122631097</v>
+        <v>122632510</v>
       </c>
       <c r="B17" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2609,42 +2560,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518656</v>
+        <v>518747</v>
       </c>
       <c r="R17" t="n">
-        <v>7077425</v>
+        <v>7077408</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2676,6 +2627,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Hackspår.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2702,12 +2658,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2725,10 +2681,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122632510</v>
+        <v>122629949</v>
       </c>
       <c r="B18" t="n">
-        <v>57494</v>
+        <v>57428</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2737,20 +2693,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>102621</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2758,25 +2714,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518747</v>
+        <v>518300</v>
       </c>
       <c r="R18" t="n">
-        <v>7077408</v>
+        <v>7077344</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2808,11 +2768,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Hackspår.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2821,31 +2776,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2862,10 +2792,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122630048</v>
+        <v>122630030</v>
       </c>
       <c r="B19" t="n">
-        <v>57428</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2874,57 +2804,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102621</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>518354</v>
+        <v>518340</v>
       </c>
       <c r="R19" t="n">
-        <v>7077408</v>
+        <v>7077417</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2959,6 +2870,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2967,6 +2883,31 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2983,10 +2924,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122629949</v>
+        <v>122630809</v>
       </c>
       <c r="B20" t="n">
-        <v>57428</v>
+        <v>57478</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2995,20 +2936,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3016,14 +2957,15 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -3032,13 +2974,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>518300</v>
+        <v>518650</v>
       </c>
       <c r="R20" t="n">
-        <v>7077344</v>
+        <v>7077436</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3070,6 +3012,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3078,6 +3025,31 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3094,10 +3066,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122632918</v>
+        <v>122630354</v>
       </c>
       <c r="B21" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3110,49 +3082,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>518775</v>
+        <v>518495</v>
       </c>
       <c r="R21" t="n">
-        <v>7077267</v>
+        <v>7077389</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3184,6 +3149,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På flera granar. Fertila bålar.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3192,6 +3162,31 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3208,10 +3203,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122630221</v>
+        <v>122631765</v>
       </c>
       <c r="B22" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3224,43 +3219,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>518418</v>
+        <v>518794</v>
       </c>
       <c r="R22" t="n">
-        <v>7077502</v>
+        <v>7077456</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3303,6 +3289,31 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3319,7 +3330,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122630171</v>
+        <v>122633093</v>
       </c>
       <c r="B23" t="n">
         <v>78766</v>
@@ -3353,24 +3364,19 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>518392</v>
+        <v>518710</v>
       </c>
       <c r="R23" t="n">
-        <v>7077379</v>
+        <v>7077368</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3402,11 +3408,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På flera granar. Vissa bålar är fertila med apothecier.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3433,12 +3434,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3456,7 +3457,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122632559</v>
+        <v>122630633</v>
       </c>
       <c r="B24" t="n">
         <v>78766</v>
@@ -3490,19 +3491,24 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>518757</v>
+        <v>518623</v>
       </c>
       <c r="R24" t="n">
-        <v>7077419</v>
+        <v>7077457</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3534,6 +3540,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Relativt rikligt. Fertila bålar.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3558,14 +3569,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3583,10 +3589,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122630505</v>
+        <v>122630221</v>
       </c>
       <c r="B25" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3599,27 +3605,31 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3628,10 +3638,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>518525</v>
+        <v>518418</v>
       </c>
       <c r="R25" t="n">
-        <v>7077442</v>
+        <v>7077502</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3674,31 +3684,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3715,10 +3700,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122630201</v>
+        <v>122633588</v>
       </c>
       <c r="B26" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3731,39 +3716,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>518443</v>
+        <v>518438</v>
       </c>
       <c r="R26" t="n">
-        <v>7077513</v>
+        <v>7077486</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3798,11 +3778,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3811,6 +3786,31 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">

--- a/artfynd/A 1-2025 artfynd.xlsx
+++ b/artfynd/A 1-2025 artfynd.xlsx
@@ -926,10 +926,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122630048</v>
+        <v>122632559</v>
       </c>
       <c r="B4" t="n">
-        <v>57428</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -938,60 +938,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102621</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518354</v>
+        <v>518757</v>
       </c>
       <c r="R4" t="n">
-        <v>7077408</v>
+        <v>7077419</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1031,6 +1012,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1047,7 +1053,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122632559</v>
+        <v>122630576</v>
       </c>
       <c r="B5" t="n">
         <v>78766</v>
@@ -1081,19 +1087,24 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518757</v>
+        <v>518557</v>
       </c>
       <c r="R5" t="n">
-        <v>7077419</v>
+        <v>7077475</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1123,6 +1134,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-16</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Långväxta bålar och relativt riklig påväxt på flera granar. Fertila bålar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1174,10 +1190,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122630576</v>
+        <v>122630201</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1190,27 +1206,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1219,13 +1235,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518557</v>
+        <v>518443</v>
       </c>
       <c r="R6" t="n">
-        <v>7077475</v>
+        <v>7077513</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1259,7 +1275,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Långväxta bålar och relativt riklig påväxt på flera granar. Fertila bålar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1270,31 +1286,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1311,10 +1302,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122630201</v>
+        <v>122632668</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1327,16 +1318,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1347,22 +1338,22 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518443</v>
+        <v>518751</v>
       </c>
       <c r="R7" t="n">
-        <v>7077513</v>
+        <v>7077424</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1396,7 +1387,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Färska hackspår som bedöms skapade inom 5 år tillbaks. I stambasen av en relativt grov gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1407,6 +1398,31 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1423,10 +1439,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122632668</v>
+        <v>122630505</v>
       </c>
       <c r="B8" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1439,42 +1455,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518751</v>
+        <v>518525</v>
       </c>
       <c r="R8" t="n">
-        <v>7077424</v>
+        <v>7077442</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1506,11 +1522,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska hackspår som bedöms skapade inom 5 år tillbaks. I stambasen av en relativt grov gran.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1537,12 +1548,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1560,10 +1571,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122630505</v>
+        <v>122631313</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1576,27 +1587,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1605,10 +1620,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518525</v>
+        <v>518757</v>
       </c>
       <c r="R9" t="n">
-        <v>7077442</v>
+        <v>7077459</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1655,26 +1670,6 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1692,10 +1687,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122631313</v>
+        <v>122630283</v>
       </c>
       <c r="B10" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1708,43 +1703,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518757</v>
+        <v>518463</v>
       </c>
       <c r="R10" t="n">
-        <v>7077459</v>
+        <v>7077394</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1791,6 +1777,26 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1808,10 +1814,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122630283</v>
+        <v>122632520</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1824,34 +1830,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518463</v>
+        <v>518841</v>
       </c>
       <c r="R11" t="n">
-        <v>7077394</v>
+        <v>7077415</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1886,6 +1897,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1894,31 +1910,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1935,10 +1926,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122632520</v>
+        <v>122629587</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>57589</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1947,20 +1938,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1968,22 +1959,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518841</v>
+        <v>518282</v>
       </c>
       <c r="R12" t="n">
-        <v>7077415</v>
+        <v>7077367</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2016,11 +2011,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-16</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2047,10 +2037,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122629587</v>
+        <v>122631097</v>
       </c>
       <c r="B13" t="n">
-        <v>57589</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2059,35 +2049,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2096,10 +2082,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518282</v>
+        <v>518656</v>
       </c>
       <c r="R13" t="n">
-        <v>7077367</v>
+        <v>7077425</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2142,6 +2128,31 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2158,7 +2169,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122631097</v>
+        <v>122630967</v>
       </c>
       <c r="B14" t="n">
         <v>78766</v>
@@ -2192,24 +2203,19 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>518656</v>
+        <v>518670</v>
       </c>
       <c r="R14" t="n">
-        <v>7077425</v>
+        <v>7077420</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2290,7 +2296,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122630967</v>
+        <v>122631152</v>
       </c>
       <c r="B15" t="n">
         <v>78766</v>
@@ -2330,13 +2336,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518670</v>
+        <v>518712</v>
       </c>
       <c r="R15" t="n">
-        <v>7077420</v>
+        <v>7077439</v>
       </c>
       <c r="S15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2417,10 +2423,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122631152</v>
+        <v>122632510</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2433,37 +2439,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518712</v>
+        <v>518747</v>
       </c>
       <c r="R16" t="n">
-        <v>7077439</v>
+        <v>7077408</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2495,6 +2506,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Hackspår.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2521,12 +2537,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2544,10 +2560,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122632510</v>
+        <v>122630354</v>
       </c>
       <c r="B17" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2560,39 +2576,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518747</v>
+        <v>518495</v>
       </c>
       <c r="R17" t="n">
-        <v>7077408</v>
+        <v>7077389</v>
       </c>
       <c r="S17" t="n">
         <v>7</v>
@@ -2629,7 +2645,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Hackspår.</t>
+          <t>På flera granar. Fertila bålar.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2658,12 +2674,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2681,10 +2697,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122629949</v>
+        <v>122630030</v>
       </c>
       <c r="B18" t="n">
-        <v>57428</v>
+        <v>78766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2693,47 +2709,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102621</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518300</v>
+        <v>518340</v>
       </c>
       <c r="R18" t="n">
-        <v>7077344</v>
+        <v>7077417</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2768,6 +2775,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2776,6 +2788,31 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2792,10 +2829,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122630030</v>
+        <v>122630809</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2808,37 +2845,47 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>518340</v>
+        <v>518650</v>
       </c>
       <c r="R19" t="n">
-        <v>7077417</v>
+        <v>7077436</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2872,7 +2919,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2901,12 +2948,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2924,10 +2971,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122630809</v>
+        <v>122631765</v>
       </c>
       <c r="B20" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2940,47 +2987,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>518650</v>
+        <v>518794</v>
       </c>
       <c r="R20" t="n">
-        <v>7077436</v>
+        <v>7077456</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3012,11 +3049,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3043,12 +3075,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3066,7 +3098,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122630354</v>
+        <v>122633093</v>
       </c>
       <c r="B21" t="n">
         <v>78766</v>
@@ -3100,21 +3132,16 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>518495</v>
+        <v>518710</v>
       </c>
       <c r="R21" t="n">
-        <v>7077389</v>
+        <v>7077368</v>
       </c>
       <c r="S21" t="n">
         <v>7</v>
@@ -3149,11 +3176,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På flera granar. Fertila bålar.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3180,12 +3202,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3203,7 +3225,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122631765</v>
+        <v>122630633</v>
       </c>
       <c r="B22" t="n">
         <v>78766</v>
@@ -3237,19 +3259,24 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>518794</v>
+        <v>518623</v>
       </c>
       <c r="R22" t="n">
-        <v>7077456</v>
+        <v>7077457</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3281,6 +3308,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Relativt rikligt. Fertila bålar.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3305,14 +3337,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3330,10 +3357,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122633093</v>
+        <v>122630221</v>
       </c>
       <c r="B23" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3346,37 +3373,46 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>518710</v>
+        <v>518418</v>
       </c>
       <c r="R23" t="n">
-        <v>7077368</v>
+        <v>7077502</v>
       </c>
       <c r="S23" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3416,31 +3452,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3457,7 +3468,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122630633</v>
+        <v>122633588</v>
       </c>
       <c r="B24" t="n">
         <v>78766</v>
@@ -3491,24 +3502,19 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>518623</v>
+        <v>518438</v>
       </c>
       <c r="R24" t="n">
-        <v>7077457</v>
+        <v>7077486</v>
       </c>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3540,11 +3546,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Relativt rikligt. Fertila bålar.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3569,9 +3570,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3589,10 +3595,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122630221</v>
+        <v>122633385</v>
       </c>
       <c r="B25" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3605,31 +3611,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3638,10 +3640,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>518418</v>
+        <v>518640</v>
       </c>
       <c r="R25" t="n">
-        <v>7077502</v>
+        <v>7077429</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3674,6 +3676,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-02-16</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3700,50 +3707,69 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122633588</v>
+        <v>122630048</v>
       </c>
       <c r="B26" t="n">
-        <v>78766</v>
+        <v>57428</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>102621</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>518438</v>
+        <v>518354</v>
       </c>
       <c r="R26" t="n">
-        <v>7077486</v>
+        <v>7077408</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3786,31 +3812,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3827,32 +3828,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122633385</v>
+        <v>122629949</v>
       </c>
       <c r="B27" t="n">
-        <v>57478</v>
+        <v>57428</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3860,10 +3861,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3872,10 +3877,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>518640</v>
+        <v>518300</v>
       </c>
       <c r="R27" t="n">
-        <v>7077429</v>
+        <v>7077344</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3908,11 +3913,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-02-16</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 1-2025 artfynd.xlsx
+++ b/artfynd/A 1-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122630171</v>
+        <v>122632559</v>
       </c>
       <c r="B2" t="n">
         <v>78766</v>
@@ -709,24 +709,19 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518392</v>
+        <v>518757</v>
       </c>
       <c r="R2" t="n">
-        <v>7077379</v>
+        <v>7077419</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-16</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På flera granar. Vissa bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -812,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122632918</v>
+        <v>122633588</v>
       </c>
       <c r="B3" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,46 +818,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518775</v>
+        <v>518438</v>
       </c>
       <c r="R3" t="n">
-        <v>7077267</v>
+        <v>7077486</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -910,6 +888,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -926,10 +929,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122632559</v>
+        <v>122629587</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>57589</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -938,41 +941,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518757</v>
+        <v>518282</v>
       </c>
       <c r="R4" t="n">
-        <v>7077419</v>
+        <v>7077367</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1012,31 +1024,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1053,7 +1040,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122630576</v>
+        <v>122633093</v>
       </c>
       <c r="B5" t="n">
         <v>78766</v>
@@ -1087,21 +1074,16 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518557</v>
+        <v>518710</v>
       </c>
       <c r="R5" t="n">
-        <v>7077475</v>
+        <v>7077368</v>
       </c>
       <c r="S5" t="n">
         <v>7</v>
@@ -1136,11 +1118,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Långväxta bålar och relativt riklig påväxt på flera granar. Fertila bålar.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1167,12 +1144,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1190,10 +1167,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122630201</v>
+        <v>122630171</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1206,27 +1183,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1235,10 +1212,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518443</v>
+        <v>518392</v>
       </c>
       <c r="R6" t="n">
-        <v>7077513</v>
+        <v>7077379</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1275,7 +1252,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På flera granar. Vissa bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1286,6 +1263,31 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1302,7 +1304,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122632668</v>
+        <v>122632510</v>
       </c>
       <c r="B7" t="n">
         <v>57494</v>
@@ -1338,7 +1340,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1347,13 +1349,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518751</v>
+        <v>518747</v>
       </c>
       <c r="R7" t="n">
-        <v>7077424</v>
+        <v>7077408</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1387,7 +1389,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Färska hackspår som bedöms skapade inom 5 år tillbaks. I stambasen av en relativt grov gran.</t>
+          <t>Hackspår.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1416,12 +1418,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1439,7 +1441,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122630505</v>
+        <v>122630030</v>
       </c>
       <c r="B8" t="n">
         <v>78766</v>
@@ -1473,21 +1475,16 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518525</v>
+        <v>518340</v>
       </c>
       <c r="R8" t="n">
-        <v>7077442</v>
+        <v>7077417</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1520,6 +1517,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-16</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1571,10 +1573,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122631313</v>
+        <v>122630201</v>
       </c>
       <c r="B9" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1587,31 +1589,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1620,10 +1618,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518757</v>
+        <v>518443</v>
       </c>
       <c r="R9" t="n">
-        <v>7077459</v>
+        <v>7077513</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1658,6 +1656,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1666,11 +1669,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1687,10 +1685,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122630283</v>
+        <v>122632520</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1703,34 +1701,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518463</v>
+        <v>518841</v>
       </c>
       <c r="R10" t="n">
-        <v>7077394</v>
+        <v>7077415</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1765,6 +1768,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1773,31 +1781,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1814,10 +1797,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122632520</v>
+        <v>122630633</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1830,42 +1813,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518841</v>
+        <v>518623</v>
       </c>
       <c r="R11" t="n">
-        <v>7077415</v>
+        <v>7077457</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1899,7 +1882,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Relativt rikligt. Fertila bålar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1910,6 +1893,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1926,10 +1929,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122629587</v>
+        <v>122631313</v>
       </c>
       <c r="B12" t="n">
-        <v>57589</v>
+        <v>57631</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1938,35 +1941,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1975,10 +1978,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518282</v>
+        <v>518757</v>
       </c>
       <c r="R12" t="n">
-        <v>7077367</v>
+        <v>7077459</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2021,6 +2024,11 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2037,10 +2045,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122631097</v>
+        <v>122630221</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2053,27 +2061,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2082,10 +2094,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518656</v>
+        <v>518418</v>
       </c>
       <c r="R13" t="n">
-        <v>7077425</v>
+        <v>7077502</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2128,31 +2140,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2169,10 +2156,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122630967</v>
+        <v>122632668</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2185,37 +2172,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>518670</v>
+        <v>518751</v>
       </c>
       <c r="R14" t="n">
-        <v>7077420</v>
+        <v>7077424</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2247,6 +2239,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska hackspår som bedöms skapade inom 5 år tillbaks. I stambasen av en relativt grov gran.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2273,12 +2270,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2423,10 +2420,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122632510</v>
+        <v>122630505</v>
       </c>
       <c r="B16" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2439,42 +2436,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518747</v>
+        <v>518525</v>
       </c>
       <c r="R16" t="n">
-        <v>7077408</v>
+        <v>7077442</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2506,11 +2503,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Hackspår.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2537,12 +2529,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2560,7 +2552,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122630354</v>
+        <v>122630967</v>
       </c>
       <c r="B17" t="n">
         <v>78766</v>
@@ -2594,21 +2586,16 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518495</v>
+        <v>518670</v>
       </c>
       <c r="R17" t="n">
-        <v>7077389</v>
+        <v>7077420</v>
       </c>
       <c r="S17" t="n">
         <v>7</v>
@@ -2641,11 +2628,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-16</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På flera granar. Fertila bålar.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2697,10 +2679,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122630030</v>
+        <v>122632918</v>
       </c>
       <c r="B18" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2713,34 +2695,46 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518340</v>
+        <v>518775</v>
       </c>
       <c r="R18" t="n">
-        <v>7077417</v>
+        <v>7077267</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2775,11 +2769,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2788,31 +2777,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2971,7 +2935,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122631765</v>
+        <v>122630283</v>
       </c>
       <c r="B20" t="n">
         <v>78766</v>
@@ -3007,14 +2971,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>518794</v>
+        <v>518463</v>
       </c>
       <c r="R20" t="n">
-        <v>7077456</v>
+        <v>7077394</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3098,7 +3062,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122633093</v>
+        <v>122631765</v>
       </c>
       <c r="B21" t="n">
         <v>78766</v>
@@ -3138,13 +3102,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>518710</v>
+        <v>518794</v>
       </c>
       <c r="R21" t="n">
-        <v>7077368</v>
+        <v>7077456</v>
       </c>
       <c r="S21" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3202,12 +3166,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3225,7 +3189,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122630633</v>
+        <v>122630354</v>
       </c>
       <c r="B22" t="n">
         <v>78766</v>
@@ -3270,10 +3234,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>518623</v>
+        <v>518495</v>
       </c>
       <c r="R22" t="n">
-        <v>7077457</v>
+        <v>7077389</v>
       </c>
       <c r="S22" t="n">
         <v>7</v>
@@ -3310,7 +3274,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Relativt rikligt. Fertila bålar.</t>
+          <t>På flera granar. Fertila bålar.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3337,9 +3301,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3357,10 +3326,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122630221</v>
+        <v>122631097</v>
       </c>
       <c r="B23" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3373,31 +3342,27 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3406,10 +3371,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>518418</v>
+        <v>518656</v>
       </c>
       <c r="R23" t="n">
-        <v>7077502</v>
+        <v>7077425</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3452,6 +3417,31 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3468,7 +3458,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122633588</v>
+        <v>122630576</v>
       </c>
       <c r="B24" t="n">
         <v>78766</v>
@@ -3502,19 +3492,24 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>518438</v>
+        <v>518557</v>
       </c>
       <c r="R24" t="n">
-        <v>7077486</v>
+        <v>7077475</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3544,6 +3539,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-02-16</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Långväxta bålar och relativt riklig påväxt på flera granar. Fertila bålar.</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 1-2025 artfynd.xlsx
+++ b/artfynd/A 1-2025 artfynd.xlsx
@@ -1441,10 +1441,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122630030</v>
+        <v>122630201</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1457,34 +1457,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518340</v>
+        <v>518443</v>
       </c>
       <c r="R8" t="n">
-        <v>7077417</v>
+        <v>7077513</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1521,7 +1526,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1532,31 +1537,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1573,10 +1553,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122630201</v>
+        <v>122630030</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1589,39 +1569,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518443</v>
+        <v>518340</v>
       </c>
       <c r="R9" t="n">
-        <v>7077513</v>
+        <v>7077417</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1658,7 +1633,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1669,6 +1644,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">

--- a/artfynd/A 1-2025 artfynd.xlsx
+++ b/artfynd/A 1-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122632559</v>
+        <v>122631152</v>
       </c>
       <c r="B2" t="n">
         <v>78766</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518757</v>
+        <v>518712</v>
       </c>
       <c r="R2" t="n">
-        <v>7077419</v>
+        <v>7077439</v>
       </c>
       <c r="S2" t="n">
         <v>8</v>
@@ -802,7 +802,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122633588</v>
+        <v>122630283</v>
       </c>
       <c r="B3" t="n">
         <v>78766</v>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518438</v>
+        <v>518463</v>
       </c>
       <c r="R3" t="n">
-        <v>7077486</v>
+        <v>7077394</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -929,10 +929,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122629587</v>
+        <v>122630576</v>
       </c>
       <c r="B4" t="n">
-        <v>57589</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -941,35 +941,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -978,13 +974,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518282</v>
+        <v>518557</v>
       </c>
       <c r="R4" t="n">
-        <v>7077367</v>
+        <v>7077475</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1016,6 +1012,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Långväxta bålar och relativt riklig påväxt på flera granar. Fertila bålar.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1024,6 +1025,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1040,7 +1066,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122633093</v>
+        <v>122630354</v>
       </c>
       <c r="B5" t="n">
         <v>78766</v>
@@ -1074,16 +1100,21 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518710</v>
+        <v>518495</v>
       </c>
       <c r="R5" t="n">
-        <v>7077368</v>
+        <v>7077389</v>
       </c>
       <c r="S5" t="n">
         <v>7</v>
@@ -1118,6 +1149,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På flera granar. Fertila bålar.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1144,12 +1180,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1167,7 +1203,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122630171</v>
+        <v>122633588</v>
       </c>
       <c r="B6" t="n">
         <v>78766</v>
@@ -1201,21 +1237,16 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518392</v>
+        <v>518438</v>
       </c>
       <c r="R6" t="n">
-        <v>7077379</v>
+        <v>7077486</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1248,11 +1279,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-16</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På flera granar. Vissa bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1304,10 +1330,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122632510</v>
+        <v>122630030</v>
       </c>
       <c r="B7" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1320,42 +1346,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518747</v>
+        <v>518340</v>
       </c>
       <c r="R7" t="n">
-        <v>7077408</v>
+        <v>7077417</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1389,7 +1410,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Hackspår.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1418,12 +1439,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1441,10 +1462,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122630201</v>
+        <v>122632918</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>57631</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1457,39 +1478,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518443</v>
+        <v>518775</v>
       </c>
       <c r="R8" t="n">
-        <v>7077513</v>
+        <v>7077267</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1522,11 +1550,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-16</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1553,10 +1576,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122630030</v>
+        <v>122632668</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1569,37 +1592,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518340</v>
+        <v>518751</v>
       </c>
       <c r="R9" t="n">
-        <v>7077417</v>
+        <v>7077424</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1633,7 +1661,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Färska hackspår som bedöms skapade inom 5 år tillbaks. I stambasen av en relativt grov gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1662,12 +1690,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1685,10 +1713,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122632520</v>
+        <v>122629587</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>57589</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1697,20 +1725,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1718,22 +1746,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518841</v>
+        <v>518282</v>
       </c>
       <c r="R10" t="n">
-        <v>7077415</v>
+        <v>7077367</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1766,11 +1798,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-16</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1797,7 +1824,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122630633</v>
+        <v>122631765</v>
       </c>
       <c r="B11" t="n">
         <v>78766</v>
@@ -1831,24 +1858,19 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518623</v>
+        <v>518794</v>
       </c>
       <c r="R11" t="n">
-        <v>7077457</v>
+        <v>7077456</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1880,11 +1902,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Relativt rikligt. Fertila bålar.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1909,9 +1926,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1929,10 +1951,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122631313</v>
+        <v>122632510</v>
       </c>
       <c r="B12" t="n">
-        <v>57631</v>
+        <v>57494</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1945,46 +1967,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518757</v>
+        <v>518747</v>
       </c>
       <c r="R12" t="n">
-        <v>7077459</v>
+        <v>7077408</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2016,6 +2034,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Hackspår.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2028,6 +2051,26 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2045,10 +2088,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122630221</v>
+        <v>122630201</v>
       </c>
       <c r="B13" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2061,31 +2104,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2094,10 +2133,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518418</v>
+        <v>518443</v>
       </c>
       <c r="R13" t="n">
-        <v>7077502</v>
+        <v>7077513</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2130,6 +2169,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-16</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2156,10 +2200,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122632668</v>
+        <v>122630633</v>
       </c>
       <c r="B14" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2172,42 +2216,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>518751</v>
+        <v>518623</v>
       </c>
       <c r="R14" t="n">
-        <v>7077424</v>
+        <v>7077457</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2241,7 +2285,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Färska hackspår som bedöms skapade inom 5 år tillbaks. I stambasen av en relativt grov gran.</t>
+          <t>Relativt rikligt. Fertila bålar.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2268,14 +2312,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2293,10 +2332,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122631152</v>
+        <v>122630809</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2309,37 +2348,47 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518712</v>
+        <v>518650</v>
       </c>
       <c r="R15" t="n">
-        <v>7077439</v>
+        <v>7077436</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2371,6 +2420,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2397,12 +2451,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2420,7 +2474,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122630505</v>
+        <v>122631097</v>
       </c>
       <c r="B16" t="n">
         <v>78766</v>
@@ -2465,10 +2519,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518525</v>
+        <v>518656</v>
       </c>
       <c r="R16" t="n">
-        <v>7077442</v>
+        <v>7077425</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2552,7 +2606,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122630967</v>
+        <v>122630171</v>
       </c>
       <c r="B17" t="n">
         <v>78766</v>
@@ -2586,19 +2640,24 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518670</v>
+        <v>518392</v>
       </c>
       <c r="R17" t="n">
-        <v>7077420</v>
+        <v>7077379</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2628,6 +2687,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-16</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På flera granar. Vissa bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2679,7 +2743,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122632918</v>
+        <v>122631313</v>
       </c>
       <c r="B18" t="n">
         <v>57631</v>
@@ -2717,24 +2781,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>permanent revir</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518775</v>
+        <v>518757</v>
       </c>
       <c r="R18" t="n">
-        <v>7077267</v>
+        <v>7077459</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2777,6 +2838,11 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2793,10 +2859,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122630809</v>
+        <v>122632559</v>
       </c>
       <c r="B19" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2809,47 +2875,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>518650</v>
+        <v>518757</v>
       </c>
       <c r="R19" t="n">
-        <v>7077436</v>
+        <v>7077419</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2881,11 +2937,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2912,12 +2963,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2935,7 +2986,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122630283</v>
+        <v>122633093</v>
       </c>
       <c r="B20" t="n">
         <v>78766</v>
@@ -2971,17 +3022,17 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>518463</v>
+        <v>518710</v>
       </c>
       <c r="R20" t="n">
-        <v>7077394</v>
+        <v>7077368</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3039,12 +3090,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3062,10 +3113,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122631765</v>
+        <v>122632520</v>
       </c>
       <c r="B21" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3078,34 +3129,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>518794</v>
+        <v>518841</v>
       </c>
       <c r="R21" t="n">
-        <v>7077456</v>
+        <v>7077415</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3140,6 +3196,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3148,31 +3209,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3189,7 +3225,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122630354</v>
+        <v>122630505</v>
       </c>
       <c r="B22" t="n">
         <v>78766</v>
@@ -3234,13 +3270,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>518495</v>
+        <v>518525</v>
       </c>
       <c r="R22" t="n">
-        <v>7077389</v>
+        <v>7077442</v>
       </c>
       <c r="S22" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3270,11 +3306,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-02-16</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På flera granar. Fertila bålar.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3326,7 +3357,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122631097</v>
+        <v>122630967</v>
       </c>
       <c r="B23" t="n">
         <v>78766</v>
@@ -3360,24 +3391,19 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Gammelgårdsbodarna, Gammelgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>518656</v>
+        <v>518670</v>
       </c>
       <c r="R23" t="n">
-        <v>7077425</v>
+        <v>7077420</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3458,10 +3484,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122630576</v>
+        <v>122630221</v>
       </c>
       <c r="B24" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3474,27 +3500,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3503,13 +3533,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>518557</v>
+        <v>518418</v>
       </c>
       <c r="R24" t="n">
-        <v>7077475</v>
+        <v>7077502</v>
       </c>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3541,11 +3571,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Långväxta bålar och relativt riklig påväxt på flera granar. Fertila bålar.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3554,31 +3579,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">

--- a/artfynd/A 1-2025 artfynd.xlsx
+++ b/artfynd/A 1-2025 artfynd.xlsx
@@ -1462,10 +1462,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122632918</v>
+        <v>122632668</v>
       </c>
       <c r="B8" t="n">
-        <v>57631</v>
+        <v>57494</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1478,49 +1478,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518775</v>
+        <v>518751</v>
       </c>
       <c r="R8" t="n">
-        <v>7077267</v>
+        <v>7077424</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1552,6 +1545,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska hackspår som bedöms skapade inom 5 år tillbaks. I stambasen av en relativt grov gran.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1560,6 +1558,31 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1576,10 +1599,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122632668</v>
+        <v>122632918</v>
       </c>
       <c r="B9" t="n">
-        <v>57494</v>
+        <v>57631</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1592,42 +1615,49 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518751</v>
+        <v>518775</v>
       </c>
       <c r="R9" t="n">
-        <v>7077424</v>
+        <v>7077267</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1659,11 +1689,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska hackspår som bedöms skapade inom 5 år tillbaks. I stambasen av en relativt grov gran.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1672,31 +1697,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -2859,10 +2859,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122632559</v>
+        <v>122632520</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2875,37 +2875,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>518757</v>
+        <v>518841</v>
       </c>
       <c r="R19" t="n">
-        <v>7077419</v>
+        <v>7077415</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2937,6 +2942,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2945,31 +2955,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2986,7 +2971,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122633093</v>
+        <v>122632559</v>
       </c>
       <c r="B20" t="n">
         <v>78766</v>
@@ -3026,13 +3011,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>518710</v>
+        <v>518757</v>
       </c>
       <c r="R20" t="n">
-        <v>7077368</v>
+        <v>7077419</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3090,12 +3075,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3113,10 +3098,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122632520</v>
+        <v>122633093</v>
       </c>
       <c r="B21" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3129,42 +3114,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>518841</v>
+        <v>518710</v>
       </c>
       <c r="R21" t="n">
-        <v>7077415</v>
+        <v>7077368</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3196,11 +3176,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3209,6 +3184,31 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">

--- a/artfynd/A 1-2025 artfynd.xlsx
+++ b/artfynd/A 1-2025 artfynd.xlsx
@@ -1462,10 +1462,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122632668</v>
+        <v>122632918</v>
       </c>
       <c r="B8" t="n">
-        <v>57494</v>
+        <v>57631</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1478,42 +1478,49 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518751</v>
+        <v>518775</v>
       </c>
       <c r="R8" t="n">
-        <v>7077424</v>
+        <v>7077267</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1545,11 +1552,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska hackspår som bedöms skapade inom 5 år tillbaks. I stambasen av en relativt grov gran.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1558,31 +1560,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1599,10 +1576,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122632918</v>
+        <v>122632668</v>
       </c>
       <c r="B9" t="n">
-        <v>57631</v>
+        <v>57494</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1615,49 +1592,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518775</v>
+        <v>518751</v>
       </c>
       <c r="R9" t="n">
-        <v>7077267</v>
+        <v>7077424</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1689,6 +1659,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska hackspår som bedöms skapade inom 5 år tillbaks. I stambasen av en relativt grov gran.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1697,6 +1672,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1824,10 +1824,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122631765</v>
+        <v>122632510</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1840,37 +1840,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518794</v>
+        <v>518747</v>
       </c>
       <c r="R11" t="n">
-        <v>7077456</v>
+        <v>7077408</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1902,6 +1907,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Hackspår.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1928,12 +1938,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1951,10 +1961,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122632510</v>
+        <v>122631765</v>
       </c>
       <c r="B12" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1967,42 +1977,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518747</v>
+        <v>518794</v>
       </c>
       <c r="R12" t="n">
-        <v>7077408</v>
+        <v>7077456</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2034,11 +2039,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Hackspår.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2065,12 +2065,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2859,10 +2859,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122632520</v>
+        <v>122632559</v>
       </c>
       <c r="B19" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2875,42 +2875,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>518841</v>
+        <v>518757</v>
       </c>
       <c r="R19" t="n">
-        <v>7077415</v>
+        <v>7077419</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2942,11 +2937,6 @@
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2955,6 +2945,31 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2971,7 +2986,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122632559</v>
+        <v>122633093</v>
       </c>
       <c r="B20" t="n">
         <v>78766</v>
@@ -3011,13 +3026,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>518757</v>
+        <v>518710</v>
       </c>
       <c r="R20" t="n">
-        <v>7077419</v>
+        <v>7077368</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3075,12 +3090,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3098,10 +3113,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122633093</v>
+        <v>122632520</v>
       </c>
       <c r="B21" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3114,37 +3129,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>518710</v>
+        <v>518841</v>
       </c>
       <c r="R21" t="n">
-        <v>7077368</v>
+        <v>7077415</v>
       </c>
       <c r="S21" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3176,6 +3196,11 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3184,31 +3209,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">

--- a/artfynd/A 1-2025 artfynd.xlsx
+++ b/artfynd/A 1-2025 artfynd.xlsx
@@ -3707,7 +3707,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122630048</v>
+        <v>122629949</v>
       </c>
       <c r="B26" t="n">
         <v>57428</v>
@@ -3742,22 +3742,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>i par</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3766,10 +3756,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>518354</v>
+        <v>518300</v>
       </c>
       <c r="R26" t="n">
-        <v>7077408</v>
+        <v>7077344</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3828,7 +3818,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122629949</v>
+        <v>122630048</v>
       </c>
       <c r="B27" t="n">
         <v>57428</v>
@@ -3863,12 +3853,22 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>i par</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>518300</v>
+        <v>518354</v>
       </c>
       <c r="R27" t="n">
-        <v>7077344</v>
+        <v>7077408</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 1-2025 artfynd.xlsx
+++ b/artfynd/A 1-2025 artfynd.xlsx
@@ -3707,7 +3707,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122629949</v>
+        <v>122630048</v>
       </c>
       <c r="B26" t="n">
         <v>57428</v>
@@ -3742,12 +3742,22 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>i par</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3756,10 +3766,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>518300</v>
+        <v>518354</v>
       </c>
       <c r="R26" t="n">
-        <v>7077344</v>
+        <v>7077408</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3818,7 +3828,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122630048</v>
+        <v>122629949</v>
       </c>
       <c r="B27" t="n">
         <v>57428</v>
@@ -3853,22 +3863,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>i par</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>518354</v>
+        <v>518300</v>
       </c>
       <c r="R27" t="n">
-        <v>7077408</v>
+        <v>7077344</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 1-2025 artfynd.xlsx
+++ b/artfynd/A 1-2025 artfynd.xlsx
@@ -3598,7 +3598,7 @@
         <v>122633385</v>
       </c>
       <c r="B25" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3707,10 +3707,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122630048</v>
+        <v>122629949</v>
       </c>
       <c r="B26" t="n">
-        <v>57428</v>
+        <v>57431</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3742,22 +3742,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>i par</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3766,10 +3756,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>518354</v>
+        <v>518300</v>
       </c>
       <c r="R26" t="n">
-        <v>7077408</v>
+        <v>7077344</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3828,10 +3818,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122629949</v>
+        <v>122630048</v>
       </c>
       <c r="B27" t="n">
-        <v>57428</v>
+        <v>57431</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3863,12 +3853,22 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>i par</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>518300</v>
+        <v>518354</v>
       </c>
       <c r="R27" t="n">
-        <v>7077344</v>
+        <v>7077408</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 1-2025 artfynd.xlsx
+++ b/artfynd/A 1-2025 artfynd.xlsx
@@ -3707,7 +3707,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122629949</v>
+        <v>122630048</v>
       </c>
       <c r="B26" t="n">
         <v>57431</v>
@@ -3742,12 +3742,22 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>i par</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3756,10 +3766,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>518300</v>
+        <v>518354</v>
       </c>
       <c r="R26" t="n">
-        <v>7077344</v>
+        <v>7077408</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3818,7 +3828,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122630048</v>
+        <v>122629949</v>
       </c>
       <c r="B27" t="n">
         <v>57431</v>
@@ -3853,22 +3863,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>i par</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>518354</v>
+        <v>518300</v>
       </c>
       <c r="R27" t="n">
-        <v>7077408</v>
+        <v>7077344</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 1-2025 artfynd.xlsx
+++ b/artfynd/A 1-2025 artfynd.xlsx
@@ -3707,7 +3707,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122630048</v>
+        <v>122629949</v>
       </c>
       <c r="B26" t="n">
         <v>57431</v>
@@ -3742,22 +3742,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>i par</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3766,10 +3756,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>518354</v>
+        <v>518300</v>
       </c>
       <c r="R26" t="n">
-        <v>7077408</v>
+        <v>7077344</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3828,7 +3818,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122629949</v>
+        <v>122630048</v>
       </c>
       <c r="B27" t="n">
         <v>57431</v>
@@ -3863,12 +3853,22 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>i par</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>518300</v>
+        <v>518354</v>
       </c>
       <c r="R27" t="n">
-        <v>7077344</v>
+        <v>7077408</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 1-2025 artfynd.xlsx
+++ b/artfynd/A 1-2025 artfynd.xlsx
@@ -3598,7 +3598,7 @@
         <v>122633385</v>
       </c>
       <c r="B25" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3707,10 +3707,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122629949</v>
+        <v>122630048</v>
       </c>
       <c r="B26" t="n">
-        <v>57431</v>
+        <v>57437</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3742,12 +3742,22 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>i par</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3756,10 +3766,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>518300</v>
+        <v>518354</v>
       </c>
       <c r="R26" t="n">
-        <v>7077344</v>
+        <v>7077408</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3818,10 +3828,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122630048</v>
+        <v>122629949</v>
       </c>
       <c r="B27" t="n">
-        <v>57431</v>
+        <v>57437</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3853,22 +3863,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>i par</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>518354</v>
+        <v>518300</v>
       </c>
       <c r="R27" t="n">
-        <v>7077408</v>
+        <v>7077344</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 1-2025 artfynd.xlsx
+++ b/artfynd/A 1-2025 artfynd.xlsx
@@ -3707,10 +3707,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122630048</v>
+        <v>122629949</v>
       </c>
       <c r="B26" t="n">
-        <v>57437</v>
+        <v>57440</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3742,22 +3742,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>i par</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3766,10 +3756,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>518354</v>
+        <v>518300</v>
       </c>
       <c r="R26" t="n">
-        <v>7077408</v>
+        <v>7077344</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3828,10 +3818,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122629949</v>
+        <v>122630048</v>
       </c>
       <c r="B27" t="n">
-        <v>57437</v>
+        <v>57440</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3863,12 +3853,22 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>i par</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>518300</v>
+        <v>518354</v>
       </c>
       <c r="R27" t="n">
-        <v>7077344</v>
+        <v>7077408</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 1-2025 artfynd.xlsx
+++ b/artfynd/A 1-2025 artfynd.xlsx
@@ -3707,10 +3707,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122629949</v>
+        <v>122630048</v>
       </c>
       <c r="B26" t="n">
-        <v>57440</v>
+        <v>57441</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3742,12 +3742,22 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>i par</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3756,10 +3766,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>518300</v>
+        <v>518354</v>
       </c>
       <c r="R26" t="n">
-        <v>7077344</v>
+        <v>7077408</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3818,10 +3828,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122630048</v>
+        <v>122629949</v>
       </c>
       <c r="B27" t="n">
-        <v>57440</v>
+        <v>57441</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3853,22 +3863,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>i par</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>518354</v>
+        <v>518300</v>
       </c>
       <c r="R27" t="n">
-        <v>7077408</v>
+        <v>7077344</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
